--- a/docs/xlsx/jobs-2026-08-24.xlsx
+++ b/docs/xlsx/jobs-2026-08-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="820">
   <si>
     <t>Title</t>
   </si>
@@ -544,24 +544,114 @@
     <t>https://www.conservationjobboard.com/job-listing-voter-registration-field-organizer-madison-wisconsin/1473533370</t>
   </si>
   <si>
+    <t>Climate Change: Cap-and-Invest Senior Market Monitor (Financial Examiner 4)</t>
+  </si>
+  <si>
+    <t>WA State Department of Ecology</t>
+  </si>
+  <si>
+    <t>Lacey, Washington, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/climate-change-cap-and-invest-senior-market-monitor-financial-examiner-4/</t>
+  </si>
+  <si>
+    <t>Senior Manager, Campaign Research</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Clean Energy</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-manager-campaign-research/</t>
+  </si>
+  <si>
+    <t>Accounting Manager</t>
+  </si>
+  <si>
+    <t>NonProfit Resources</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/047a20d4aff9470d803b720b29eb7206-accounting-manager-nonprofit-resources-rapid-city</t>
+  </si>
+  <si>
+    <t>Admin &amp; Support Instructor</t>
+  </si>
+  <si>
+    <t>Skybil</t>
+  </si>
+  <si>
+    <t>Remote (NG)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>NGN 1000000.00/month</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/community-job/301b646ff52d410f97a3624a9c123cee-admin-support-instructor-skybil-ondo</t>
+  </si>
+  <si>
+    <t>Administrative Assistant (Hybrid)</t>
+  </si>
+  <si>
+    <t>Basel Action Network</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb7ab6da9c1b49c390b34ad24ecaf417-administrative-assistant-hybrid-basel-action-network-seattle</t>
+  </si>
+  <si>
+    <t>Administrative Contractor</t>
+  </si>
+  <si>
+    <t>The Diabetes Link</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9cb118b60cd848a3b220f43375a5a4bf-administrative-contractor-the-diabetes-link-boston</t>
+  </si>
+  <si>
     <t>Administrative Contractor (REMOTE)</t>
   </si>
   <si>
-    <t>The Diabetes Link</t>
-  </si>
-  <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>Contract</t>
-  </si>
-  <si>
-    <t>USD 20.00 - 25.00/hour</t>
-  </si>
-  <si>
-    <t>Disability, Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9cb118b60cd848a3b220f43375a5a4bf-administrative-contractor-remote-the-diabetes-link-boston</t>
   </si>
   <si>
@@ -574,9 +664,6 @@
     <t>Kinston, North Carolina</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 43000.00 - 52000.00/year</t>
   </si>
   <si>
@@ -586,6 +673,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/3a5b02aff06d4011a7d651f36a4381bf-administrative-manager-kinston-teens-inc-kinston</t>
   </si>
   <si>
+    <t>Advancement Director, Tennessee and Kentucky Chapter</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Remote (Tennessee)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2aec9a5e8c94344ac51c6c88a485017-advancement-director-tennessee-and-kentucky-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>After School Academic Program Manager</t>
+  </si>
+  <si>
+    <t>Zone 126</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8ef58c5fa6c45a0918e7160083219e3-after-school-academic-program-manager-zone-126-queens-county</t>
+  </si>
+  <si>
     <t>After School Group Leader - Per Diem</t>
   </si>
   <si>
@@ -595,9 +718,6 @@
     <t>New York, New York</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 20.00 - 24.00/hour</t>
   </si>
   <si>
@@ -607,6 +727,324 @@
     <t>https://www.idealist.org/en/nonprofit-job/3ad5a2b1b88f46b79675e5efaafc3ab6-after-school-group-leader-per-diem-the-ywca-of-the-city-of-new-york-new-york</t>
   </si>
   <si>
+    <t>Aftercare Operations Specialist</t>
+  </si>
+  <si>
+    <t>Anthos Home</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61b884de588440fe856bbc67df8dcb39-aftercare-operations-specialist-anthos-home-new-york</t>
+  </si>
+  <si>
+    <t>Afterschool Program Coordinator</t>
+  </si>
+  <si>
+    <t>the haus of performing arts</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d565f6ee055c4991b9c7d82c134e2b6a-afterschool-program-coordinator-the-haus-of-performing-arts-bronx-county</t>
+  </si>
+  <si>
+    <t>AG Fellowship Program: Post-Grad Opportunity 3L Law Students</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>USD 87356.00 - 91356.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/e9af02b69aec47e69551d258f9eae7d0-ag-fellowship-program-post-grad-opportunity-3l-law-students-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Director of Health Center Optimization</t>
+  </si>
+  <si>
+    <t>California Primary Care Association</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a9e44a3f77e14ee6963b3070833cb8d2-assistant-director-of-health-center-optimization-california-primary-care-association-sacramento</t>
+  </si>
+  <si>
+    <t>Assistant Livestock Manager</t>
+  </si>
+  <si>
+    <t>Glynwood Center for Regional Food and Farming</t>
+  </si>
+  <si>
+    <t>Cold Spring, New York</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1f501110cb19414eb94e490603898b41-assistant-livestock-manager-glynwood-center-for-regional-food-and-farming-cold-spring</t>
+  </si>
+  <si>
+    <t>Attendance Success Coordinator - Elementary</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afb1169440aa444686c7332cd653f5dd-attendance-success-coordinator-elementary-zone-126-queens-county</t>
+  </si>
+  <si>
+    <t>Business Training Manager - Waltham</t>
+  </si>
+  <si>
+    <t>More Than Words</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 57749.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/f6c3007d91914d568263293b34581f5a-business-training-manager-waltham-more-than-words-waltham</t>
+  </si>
+  <si>
+    <t>Camp Director</t>
+  </si>
+  <si>
+    <t>Hashomer Hatzair / Camp Shomria</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc19f693bf934166a2f3c39a182a2a50-camp-director-hashomer-hatzair-camp-shomria-new-york</t>
+  </si>
+  <si>
+    <t>Civic Science Fellow, Evidence &amp; Creator Partnerships</t>
+  </si>
+  <si>
+    <t>AcademyHealth</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48efac30346a427ca518db03fe783b9b-civic-science-fellow-evidence-creator-partnerships-academyhealth-washington</t>
+  </si>
+  <si>
+    <t>Civil Rights Attorney</t>
+  </si>
+  <si>
+    <t>Law Office of Fred Lichtmacher</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/8ac8cc751e344a7ab17f45c07f9fad82-civil-rights-attorney-law-office-of-fred-lichtmacher-new-york</t>
+  </si>
+  <si>
+    <t>Washington State Department of Ecology</t>
+  </si>
+  <si>
+    <t>Lacey, Washington</t>
+  </si>
+  <si>
+    <t>USD 91104.00 - 122460.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/8da90b3e8be2448d9ae01943e353aa38-climate-change-cap-and-invest-senior-market-monitor-financial-examiner-4-washington-state-department-of-ecology-lacey</t>
+  </si>
+  <si>
+    <t>COLLEGE ACCESS PROGRAM ADVISOR – WOONSOCKET HIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>College Visions</t>
+  </si>
+  <si>
+    <t>Woonsocket, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8558835446234fa5b1b4005a315f61db-college-access-program-advisor-woonsocket-high-school-college-visions-woonsocket</t>
+  </si>
+  <si>
+    <t>Community Development Manager</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Community Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f041f096582f4a82be85bceaba96de10-community-development-manager-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Community Engagement &amp; Action Coordinator</t>
+  </si>
+  <si>
+    <t>Community Council</t>
+  </si>
+  <si>
+    <t>Walla Walla, Washington</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 99000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1eefef6b72540ebab161fc149296d75-community-engagement-action-coordinator-community-council-walla-walla</t>
+  </si>
+  <si>
+    <t>Community Roots Charter School, Academic Interventionist, Grades 6-8, 2026-2027</t>
+  </si>
+  <si>
+    <t>Community Roots Charter School</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 65894.00 - 121360.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e83f5d714b7a4a7da767dc161f04e35d-community-roots-charter-school-academic-interventionist-grades-6-8-2026-2027-community-roots-charter-school-kings-county</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Meals on Wheels People, Inc.</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 113600.00 - 153600.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b68cfbe2d1e3455cabeee0eaab96c6c0-controller-meals-on-wheels-people-inc-portland</t>
+  </si>
+  <si>
+    <t>Corporate Relations Manager</t>
+  </si>
+  <si>
+    <t>Fish &amp; Wildlife Foundation of Florida, Inc.</t>
+  </si>
+  <si>
+    <t>Tallahassee, Florida</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d3914b0230944c7a628700a9eed5ebe-corporate-relations-manager-fish-wildlife-foundation-of-florida-inc-tallahassee</t>
+  </si>
+  <si>
+    <t>Data Science Program Assistant/College Assistant</t>
+  </si>
+  <si>
+    <t>CUNY School of Professional Studies</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b3122f2e968c490691023956953bc4ee-data-science-program-assistantcollege-assistant-cuny-school-of-professional-studies-new-york</t>
+  </si>
+  <si>
+    <t>Defensive Program Director</t>
+  </si>
+  <si>
+    <t>Oasis Legal Services</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 94000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf1e3cf41e0b4251b7a31da2a3640b9b-defensive-program-director-oasis-legal-services-berkeley</t>
+  </si>
+  <si>
+    <t>Dentista de Projetos</t>
+  </si>
+  <si>
+    <t>Turma do Bem</t>
+  </si>
+  <si>
+    <t>São Paulo, São Paulo, BR</t>
+  </si>
+  <si>
+    <t>BRL 4500.00 - 4500.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f962e83023742ecbbb717ebb4641f76-dentista-de-projetos-turma-do-bem-sao-paulo</t>
+  </si>
+  <si>
+    <t>Deputy Director</t>
+  </si>
+  <si>
+    <t>SF New Deal</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe531380ec1d4a8bb568a7cedd206a82-deputy-director-sf-new-deal-san-francisco</t>
+  </si>
+  <si>
     <t>Development &amp; Administrative Associate</t>
   </si>
   <si>
@@ -622,6 +1060,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/106f1f6ccb2944039228b8f9966455a1-development-administrative-associate-new-yorkers-for-parks-new-york</t>
   </si>
   <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>Jesuit Volunteer Corps</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Entrepreneurship, Religion Spirituality, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40e9007da7304807add012ef719f2492-development-associate-jesuit-volunteer-corps-baltimore</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6673158b3f2544afbe724d856333a9e1-development-associate-anthos-home-new-york</t>
+  </si>
+  <si>
     <t>Development Associate / Office Manager</t>
   </si>
   <si>
@@ -640,6 +1099,84 @@
     <t>https://www.idealist.org/en/nonprofit-job/561a0df0f5574d71b4c818cf2be9bc76-development-associate-office-manager-mission-doctors-association-los-angeles</t>
   </si>
   <si>
+    <t>Development Coordinator – New Jersey Pennsylvania Chapter</t>
+  </si>
+  <si>
+    <t>Remote (New Jersey)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ed6efc06e1643389fc48c42a3c76d21-development-coordinator-new-jersey-pennsylvania-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Development Coordinator (Environmental Nonprofit, Major Gifts)</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1f2101ab40fd45b4856e721a1793283e-development-coordinator-environmental-nonprofit-major-gifts-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>San Francisco Zoo &amp; Gardens</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05b592bf85c34ae1808dcc8223bc458b-development-manager-san-francisco-zoo-gardens-san-francisco</t>
+  </si>
+  <si>
+    <t>Development Manager (On-Site)</t>
+  </si>
+  <si>
+    <t>Young People's Chorus of NYC</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21da64a4ca4845f4b3149a586007e403-development-manager-on-site-young-peoples-chorus-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Development Manager, North America</t>
+  </si>
+  <si>
+    <t>Room to Read</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 106000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/01532bc2f6fe47c18ec3671258baafcf-development-manager-north-america-room-to-read-san-francisco</t>
+  </si>
+  <si>
+    <t>Digital Marketing Instructor</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/community-job/86ec17302a3343f1805a8eb7926dbb67-digital-marketing-instructor-skybil-ondo</t>
+  </si>
+  <si>
     <t>Director of Communications &amp; Public Relations</t>
   </si>
   <si>
@@ -655,6 +1192,75 @@
     <t>https://www.idealist.org/en/nonprofit-job/ffa7921c50e04078b5b5fe617e4f9d34-director-of-communications-public-relations-project-equity-oakland</t>
   </si>
   <si>
+    <t>Director of Field Operations</t>
+  </si>
+  <si>
+    <t>Minnesota Nurses Association</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 159991.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bab090538ed94defa9be15fc2aa54c50-director-of-field-operations-minnesota-nurses-association-saint-paul</t>
+  </si>
+  <si>
+    <t>Director of Foundation and Corporate Relations</t>
+  </si>
+  <si>
+    <t>Save The Bay</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 116701.00 - 116701.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ad5a8257c9e463b91374e5ce7e2cdd8-director-of-foundation-and-corporate-relations-save-the-bay-oakland</t>
+  </si>
+  <si>
+    <t>Director of Human Resources (HR)</t>
+  </si>
+  <si>
+    <t>The SEED Foundation</t>
+  </si>
+  <si>
+    <t>USD 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9659b64ea80e48b39665f827101af06b-director-of-human-resources-hr-the-seed-foundation-washington</t>
+  </si>
+  <si>
+    <t>Director of Impact</t>
+  </si>
+  <si>
+    <t>Chicago HOPES for Kids</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ea0b46bbb3d40b7913fa61684d8bcc6-director-of-impact-chicago-hopes-for-kids-chicago</t>
+  </si>
+  <si>
     <t>Director of Marketing &amp; Engagement</t>
   </si>
   <si>
@@ -670,15 +1276,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/de6d402b05104b65a61ce994547168c7-director-of-marketing-engagement-lincoln-square-business-improvement-district-new-york</t>
   </si>
   <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Partnership for the Advancement and Immersion of Refugees</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03575a2f735b40ae9ceec89f5dd47ee7-director-of-programs-partnership-for-the-advancement-and-immersion-of-refugees-houston</t>
+  </si>
+  <si>
     <t>Director of Public Policy and Government Relations</t>
   </si>
   <si>
     <t>Alliance for Aging Research</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 90000.00 - 95000.00/year</t>
   </si>
   <si>
@@ -700,12 +1318,93 @@
     <t>USD 100000.00 - 105000.00/year</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/8db422ad0ea64622b74b0d1d91e99dbe-director-clearinghouse-services-health-resources-in-action-inc-boston</t>
   </si>
   <si>
+    <t>Distributed Organizer Contractor</t>
+  </si>
+  <si>
+    <t>New Advocacy Organization for AI Regulation</t>
+  </si>
+  <si>
+    <t>USD 2000.00 - 2000.00/week</t>
+  </si>
+  <si>
+    <t>Policy, Science Technology, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f5fb7783c144265aede1b85e36e7a42-distributed-organizer-contractor-new-advocacy-organization-for-ai-regulation-new-york</t>
+  </si>
+  <si>
+    <t>Donor Relations Coordinator, Miami</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be0f3b2ee8144ef08f6a8213c715881c-donor-relations-coordinator-miami-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Donor Relations Coordinator, New York</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/51bea4a94d3042fdb0d84dfcd1b54e7f-donor-relations-coordinator-new-york-parkinsons-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Education Director - Early Childhood Education</t>
+  </si>
+  <si>
+    <t>YM &amp; YWHA of Washington Heights and Inwood</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6aa588f2eb07424991ec500af7d43945-education-director-early-childhood-education-ym-ywha-of-washington-heights-and-inwood-new-york</t>
+  </si>
+  <si>
+    <t>Employment Case Manager</t>
+  </si>
+  <si>
+    <t>Syrian Community Network</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>USD 45760.00 - 45760.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80d76f5436f540219845ce6733890171-employment-case-manager-syrian-community-network-chicago</t>
+  </si>
+  <si>
+    <t>Enterprise Portfolio Manager</t>
+  </si>
+  <si>
+    <t>Craftsman Technology Group</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Climate Change, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2f4761bd5e1e45d2b4ce36d61f4f85c7-enterprise-portfolio-manager-craftsman-technology-group-boston</t>
+  </si>
+  <si>
     <t>Entry Level Digital Specialist</t>
   </si>
   <si>
@@ -754,12 +1453,75 @@
     <t>USD 160000.00 - 200000.00/year</t>
   </si>
   <si>
-    <t>Arts Music, Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/f46e2a0055dc40b5902b58bcda9e0c3a-executive-director-artsconnection-new-york</t>
   </si>
   <si>
+    <t>Oregon Consumer Justice</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4567c035cb884abb908bc4a3fc7b85f5-executive-director-oregon-consumer-justice-portland</t>
+  </si>
+  <si>
+    <t>Bronzeville Wellness Collective</t>
+  </si>
+  <si>
+    <t>USD 165000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/381f42f9713d41719971ed5a0eef1753-executive-director-bronzeville-wellness-collective-chicago</t>
+  </si>
+  <si>
+    <t>Southern Delaware Therapeutic &amp; Recreational Horseback Riding, Inc.</t>
+  </si>
+  <si>
+    <t>Milton, Delaware</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Children Youth, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e225691bcb648ffb52af398dcefbf99-executive-director-southern-delaware-therapeutic-recreational-horseback-riding-inc-milton</t>
+  </si>
+  <si>
+    <t>EXECUTIVE DIRECTOR</t>
+  </si>
+  <si>
+    <t>Rise-NY</t>
+  </si>
+  <si>
+    <t>Endicott, New York</t>
+  </si>
+  <si>
+    <t>Crime Safety, Housing Homelessness, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/56868f4f87aa430fb49c880cf7ef5b7c-executive-director-rise-ny-endicott</t>
+  </si>
+  <si>
+    <t>Executive Director, Amigos Bravos</t>
+  </si>
+  <si>
+    <t>Amigos Bravos</t>
+  </si>
+  <si>
+    <t>Taos, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Water Sanitation, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f2100ff2afe40cf8f96280ffb91827e-executive-director-amigos-bravos-amigos-bravos-taos</t>
+  </si>
+  <si>
     <t>Executive Director, Franklin County Community Meals Program</t>
   </si>
   <si>
@@ -781,6 +1543,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/6b2d0d854b6f4169ad332a62dcc429cd-executive-director-franklin-county-community-meals-program-franklin-county-community-meals-program-inc-greenfield</t>
   </si>
   <si>
+    <t>Executive Director, WISE</t>
+  </si>
+  <si>
+    <t>Eos Transition Partners</t>
+  </si>
+  <si>
+    <t>Lebanon, New Hampshire</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/4f53ef071f21454384956facd5e21619-executive-director-wise-eos-transition-partners-lebanon</t>
+  </si>
+  <si>
     <t>Finance &amp; Development Coordinator</t>
   </si>
   <si>
@@ -817,6 +1597,126 @@
     <t>https://www.idealist.org/en/nonprofit-job/b939f03b3b434070891e68866d3034cf-finance-and-administrative-coordinator-growing-hope-globally-western-springs</t>
   </si>
   <si>
+    <t>Full-Time Psychotherapist</t>
+  </si>
+  <si>
+    <t>Community Counseling and Mediation</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/86a55bf003cf4afca6f674fb329479ff-full-time-psychotherapist-community-counseling-and-mediation-kings-county</t>
+  </si>
+  <si>
+    <t>Fundraising Events Coordinator</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4378a7ca19a54f929fc4ac3915e4764d-fundraising-events-coordinator-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Fundraising Events Specialist</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/402b97ecc8324a50ba39c4ada002d70f-fundraising-events-specialist-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Gift Planning Coordinator</t>
+  </si>
+  <si>
+    <t>The Huntington Library, Art Museum, and Botanical Gardens</t>
+  </si>
+  <si>
+    <t>San Marino, California</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/894de5ac96b845369af9beba8d7abdfd-gift-planning-coordinator-the-huntington-library-art-museum-and-botanical-gardens-san-marino</t>
+  </si>
+  <si>
+    <t>Government Programs Coordinator</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e2dbb36cf014757995492a3cac508b2-government-programs-coordinator-fish-wildlife-foundation-of-florida-inc-tallahassee</t>
+  </si>
+  <si>
+    <t>Grants and Client Partnerships Lead</t>
+  </si>
+  <si>
+    <t>Sommer Neff Consulting</t>
+  </si>
+  <si>
+    <t>Remote (Plano, Texas)</t>
+  </si>
+  <si>
+    <t>USD 3000.00 - 3500.00/month</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/272a0aaf7b1f4994bc27305faae20418-grants-and-client-partnerships-lead-sommer-neff-consulting-plano</t>
+  </si>
+  <si>
+    <t>Group and Corporate Fundraising Manager</t>
+  </si>
+  <si>
+    <t>Make-A-Wish Greater Los Angeles</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/51a6bf5c4b404ad2ae436b06cac35509-group-and-corporate-fundraising-manager-make-a-wish-greater-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Human Resources Associate</t>
+  </si>
+  <si>
+    <t>USD 32.90 - 32.90/hour</t>
+  </si>
+  <si>
+    <t>Job Workplace, Policy, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/81d32be1e8054a989ecb28c86b49a83a-human-resources-associate-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Interim Producing Director</t>
+  </si>
+  <si>
+    <t>CounterPulse</t>
+  </si>
+  <si>
+    <t>USD 45.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Lgbtq, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0c2faa277164af4b04cc0ede559e778-interim-producing-director-counterpulse-san-francisco</t>
+  </si>
+  <si>
     <t>Lead - Impact Evaluation, Mumbai</t>
   </si>
   <si>
@@ -859,18 +1759,21 @@
     <t>East Side House Settlement</t>
   </si>
   <si>
-    <t>Bronx County, New York</t>
-  </si>
-  <si>
-    <t>USD 60000.00 - 60000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Education, Science Technology</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/04493614f4f94c4eb52ea36e3bd0e9f7-ltw-assistant-director-internship-coordinator-east-side-house-settlement-bronx-county</t>
   </si>
   <si>
+    <t>Major Gift Officer</t>
+  </si>
+  <si>
+    <t>Land Trust Alliance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4e5cc6daede4cdcb8c092be03ea9f94-major-gift-officer-land-trust-alliance-washington</t>
+  </si>
+  <si>
     <t>Manager, Africa &amp; Middle East</t>
   </si>
   <si>
@@ -886,6 +1789,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/7d1e6a348dad4ec38f56145c55a21e22-manager-africa-middle-east-myriad-usa-new-york</t>
   </si>
   <si>
+    <t>Managing Attorney, Family Law Practice (Domestic Violence Program)</t>
+  </si>
+  <si>
+    <t>Volunteer Legal Advocates</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Legal Assistance, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e54c31b96eb424389912a8a384e47e3-managing-attorney-family-law-practice-domestic-violence-program-volunteer-legal-advocates-washington</t>
+  </si>
+  <si>
     <t>Managing Editor</t>
   </si>
   <si>
@@ -916,6 +1834,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/53c571bd819b44fbb482122d60e21c4e-marketing-and-communications-manager-st-francis-house-boston</t>
   </si>
   <si>
+    <t>Marketing Manager</t>
+  </si>
+  <si>
+    <t>The Oakland Zoo</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>USD 71770.36 - 83203.03/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c596d90ab3f049a7a8fe7184ee4a3f4f-marketing-manager-the-oakland-zoo-oakland</t>
+  </si>
+  <si>
     <t>Médico/a General</t>
   </si>
   <si>
@@ -952,15 +1888,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/6d4e06c0e0c74e40bcb854e768178657-njsacc-seeks-part-time-legislative-policy-consultant-njsacc-new-jerseys-afterschool-and-out-of-school-time-professional-network-westfield</t>
   </si>
   <si>
+    <t>Nonprofit Board Member — MC917 Foundation, Inc. (Unpaid, Remote/Flexible)</t>
+  </si>
+  <si>
+    <t>MC917 Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>Wilmington, Delaware</t>
+  </si>
+  <si>
+    <t>USD 0.00 - 0.00/year</t>
+  </si>
+  <si>
+    <t>Volunteering, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94e170379da746a7b0bdee04d24d4aa7-nonprofit-board-member-mc917-foundation-inc-unpaid-remoteflexible-mc917-foundation-inc-wilmington</t>
+  </si>
+  <si>
     <t>O4A Fellow</t>
   </si>
   <si>
     <t>4A American Alliance of Artists &amp; Audiences (4A Arts)</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
     <t>Arts Music, Civic Engagement</t>
   </si>
   <si>
@@ -979,6 +1930,102 @@
     <t>https://www.idealist.org/en/nonprofit-job/315d717fb9034ac49c8a0e7407bb8c69-office-assistant-part-time-t-w-th-900-am-400-pm-american-association-of-colleges-of-nursing-washington</t>
   </si>
   <si>
+    <t>Office of Developmental Disabilities Ombuds Region 3 DD Ombuds</t>
+  </si>
+  <si>
+    <t>Disability Rights Washington</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 73759.00 - 81416.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0dd48dfab2ff4b6d9e799da16e07a5b8-office-of-developmental-disabilities-ombuds-region-3-dd-ombuds-disability-rights-washington-seattle</t>
+  </si>
+  <si>
+    <t>Operario de depósito</t>
+  </si>
+  <si>
+    <t>Banco de Alimentos</t>
+  </si>
+  <si>
+    <t>Benavidez, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e781e4a236f24313b1da2bd393181420-operario-de-deposito-banco-de-alimentos-benavidez</t>
+  </si>
+  <si>
+    <t>Operations Associate</t>
+  </si>
+  <si>
+    <t>Second Stage Theater</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9de578985ac049fe858115369f211418-operations-associate-second-stage-theater-new-york</t>
+  </si>
+  <si>
+    <t>Outreach and Education Specialist</t>
+  </si>
+  <si>
+    <t>Greater Community AIDS Project of East Central Illinois (GCAP)</t>
+  </si>
+  <si>
+    <t>Champaign, Illinois</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4839ca201a1c47d18b5efd910812401d-outreach-and-education-specialist-greater-community-aids-project-of-east-central-illinois-gcap-champaign</t>
+  </si>
+  <si>
+    <t>Outreach Coordinator II (Northern California- )</t>
+  </si>
+  <si>
+    <t>Center for Caregiver Advancement</t>
+  </si>
+  <si>
+    <t>Northern, California</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 70304.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Human Rights Civil Liberties, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f13a9bd5bdd14340a7085b5b4b502cb9-outreach-coordinator-ii-northern-california-center-for-caregiver-advancement-northern</t>
+  </si>
+  <si>
+    <t>Philanthropy Officer - Individual Giving</t>
+  </si>
+  <si>
+    <t>Arts Impact</t>
+  </si>
+  <si>
+    <t>Cleveland, Ohio</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6a182cf0af04e57b33669e9253336ee-philanthropy-officer-individual-giving-arts-impact-cleveland</t>
+  </si>
+  <si>
     <t>Physical Therapist in Belize</t>
   </si>
   <si>
@@ -1042,6 +2089,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/2329a5d3ebfa4cc08acb63550bdc764c-programs-coordinator-fiscal-systems-lincoln-institute-of-land-policy-cambridge</t>
   </si>
   <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/040159e5927941e18a4a791dfe70fc06-project-manager-sf-new-deal-san-francisco</t>
+  </si>
+  <si>
     <t>Project Manager - Ukraine</t>
   </si>
   <si>
@@ -1069,15 +2122,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/ccdb3e6b4e5d4eef8844bf026e001662-project-manager-ukraine-intersos-mykolaiv</t>
   </si>
   <si>
+    <t>Recovery Manager</t>
+  </si>
+  <si>
+    <t>National Alliance on Mental Illness (NAMI) Chicago</t>
+  </si>
+  <si>
+    <t>Education, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e73844f9d53544f18e0879781d6d7d3a-recovery-manager-national-alliance-on-mental-illness-nami-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Regranting and Partner Support Assistant</t>
+  </si>
+  <si>
+    <t>Environmental Law Alliance Worldwide</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Human Rights Civil Liberties, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57cb7ad45a5f4e1185df7425136f31f4-regranting-and-partner-support-assistant-environmental-law-alliance-worldwide-eugene</t>
+  </si>
+  <si>
     <t>Resilience - Executive Director</t>
   </si>
   <si>
     <t>Resilience</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>USD 150000.00 - 165000.00/year</t>
   </si>
   <si>
@@ -1087,6 +2164,114 @@
     <t>https://www.idealist.org/en/job/e3622c1500ce437589bcd33e3ec5df78-resilience-executive-director-resilience-chicago</t>
   </si>
   <si>
+    <t>Senior Case Worker</t>
+  </si>
+  <si>
+    <t>Ashiyanaa</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efce1848dd6143cab4568bc8af95b848-senior-case-worker-ashiyanaa-washington</t>
+  </si>
+  <si>
+    <t>Senior Development Coordinator – California Chapter</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30e94f7a18bd453895389dccad712640-senior-development-coordinator-california-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Senior Development Manager</t>
+  </si>
+  <si>
+    <t>USD 75400.00 - 102000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Volunteering, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e36e2e54c0f2429d9d08341242cc3b3a-senior-development-manager-meals-on-wheels-people-inc-portland</t>
+  </si>
+  <si>
+    <t>Senior Director of Development and Communications</t>
+  </si>
+  <si>
+    <t>NC Child</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8fe2b03b365c435792fcf8a3169789ef-senior-director-of-development-and-communications-nc-child-raleigh</t>
+  </si>
+  <si>
+    <t>Senior Program Associate</t>
+  </si>
+  <si>
+    <t>Bring Change to Mind</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54894e018c8b4e98bdc596d41c6bee28-senior-program-associate-bring-change-to-mind-san-francisco</t>
+  </si>
+  <si>
+    <t>Service Enriched Housing Super Hero</t>
+  </si>
+  <si>
+    <t>Community Housing Resource Partners, Inc.</t>
+  </si>
+  <si>
+    <t>San Antonio, Texas</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a324320ef2d848acb9010bd054daf614-service-enriched-housing-super-hero-community-housing-resource-partners-inc-san-antonio</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a820b76547f4854b242030b727c17cd-service-enriched-housing-super-hero-community-housing-resource-partners-inc-austin</t>
+  </si>
+  <si>
+    <t>Southeastern Washington Organizer</t>
+  </si>
+  <si>
+    <t>Washington Youth Alliance</t>
+  </si>
+  <si>
+    <t>Pasco, Washington</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e37a81b53fa4ae9ad3dec772ba83c14-southeastern-washington-organizer-washington-youth-alliance-pasco</t>
+  </si>
+  <si>
     <t>Special Collections Librarian</t>
   </si>
   <si>
@@ -1105,6 +2290,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/28ff47bb64794ecf9e5e762d1e1bc6f0-special-collections-librarian-fairfield-museum-and-history-center-fairfield</t>
   </si>
   <si>
+    <t>Sr. Workplace Support Specialist (2-year term)</t>
+  </si>
+  <si>
+    <t>The Wilderness Society</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a12b68b047314df080657a2b87afc998-sr-workplace-support-specialist-2-year-term-the-wilderness-society-denver</t>
+  </si>
+  <si>
     <t>Staff Attorney, Immigration Project</t>
   </si>
   <si>
@@ -1123,6 +2320,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/7a69cea40c38427e86a135c747899565-staff-attorney-immigration-project-volunteers-of-legal-service-new-york</t>
   </si>
   <si>
+    <t>Temporary Paralegal</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 67793.00 - 72442.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bb0f1bfc55a4eb395833e5fe0026c92-temporary-paralegal-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Town of Chatham - DPW Highway Division - Heavy Equipment Operator/Vehicle Mechanic</t>
+  </si>
+  <si>
+    <t>Town of Chatham, MA</t>
+  </si>
+  <si>
+    <t>Chatham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 61068.80 - 63544.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/d9e9cf7ffe464e9497fb96efb5077d99-town-of-chatham-dpw-highway-division-heavy-equipment-operatorvehicle-mechanic-town-of-chatham-ma-chatham</t>
+  </si>
+  <si>
+    <t>Town of Chatham - Transfer Station Division - Heavy Equipment Operator</t>
+  </si>
+  <si>
+    <t>USD 61068.80 - 66081.60/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/25be8d68b1e44a4bbf586fd1e9cf40fe-town-of-chatham-transfer-station-division-heavy-equipment-operator-town-of-chatham-ma-chatham</t>
+  </si>
+  <si>
     <t>Training Manager</t>
   </si>
   <si>
@@ -1136,6 +2372,99 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/7db59717b2a14c4cb77a8013408916a3-training-manager-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Tutor</t>
+  </si>
+  <si>
+    <t>Southeast Community Foundation</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c47866c4333a4e439bbbb0c404a30f9b-tutor-southeast-community-foundation-los-angeles</t>
+  </si>
+  <si>
+    <t>Union Organizer (Internal Public Sector)</t>
+  </si>
+  <si>
+    <t>SEIU Local 503, OPEU</t>
+  </si>
+  <si>
+    <t>Salem, Oregon</t>
+  </si>
+  <si>
+    <t>USD 68136.00 - 101268.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f5d8e51911d450091b232ad372ff86b-union-organizer-internal-public-sector-seiu-local-503-opeu-salem</t>
+  </si>
+  <si>
+    <t>Vice President of Philanthropy</t>
+  </si>
+  <si>
+    <t>Crazy Horse Memorial Foundation</t>
+  </si>
+  <si>
+    <t>Custer, South Dakota</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Race Ethnicity, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09baae1bd4e9444ebea0b2003c35e9d7-vice-president-of-philanthropy-crazy-horse-memorial-foundation-custer</t>
+  </si>
+  <si>
+    <t>We're Hiring Field Directors in Nebraska!</t>
+  </si>
+  <si>
+    <t>The Outreach Team</t>
+  </si>
+  <si>
+    <t>Nebraska City, Nebraska</t>
+  </si>
+  <si>
+    <t>USD 1146.00 - 1500.00/week</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/716abce58c7449acb731731d217d6034-were-hiring-field-directors-in-nebraska-the-outreach-team-nebraska-city</t>
+  </si>
+  <si>
+    <t>Fremont, Nebraska</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/341bafca8b6547e1b97651dbdbcb1a3b-were-hiring-field-directors-in-nebraska-the-outreach-team-fremont</t>
+  </si>
+  <si>
+    <t>Writing &amp; Content Instructor</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/community-job/c4ed6c78615a4317b238729bb5e98975-writing-content-instructor-skybil-ondo</t>
+  </si>
+  <si>
+    <t>Youth Development Specialist</t>
+  </si>
+  <si>
+    <t>Fab Youth Philly</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8ca0b35938f74fc496018f7a9333e45d-youth-development-specialist-fab-youth-philly-philadelphia</t>
   </si>
   <si>
     <t>Youth Educator, Patterson School Year 2026-27</t>
@@ -2348,7 +3677,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2387,8 +3716,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2396,7 +3775,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2437,384 +3816,384 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" t="s">
         <v>180</v>
       </c>
-      <c r="F2" t="s">
-        <v>181</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="F3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D4" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E4" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="F4" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F5" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B6" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B7" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F8" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B9" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E9" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F9" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B10" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C10" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E10" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F10" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B11" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F11" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B12" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F12" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B13" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E13" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F13" t="s">
-        <v>242</v>
+        <v>180</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B14" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E14" t="s">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="F14" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B15" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C15" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D15" t="s">
-        <v>251</v>
+        <v>190</v>
       </c>
       <c r="E15" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F15" t="s">
-        <v>253</v>
+        <v>180</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B16" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="C16" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="D16" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="F16" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B17" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D17" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E17" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F17" t="s">
-        <v>265</v>
+        <v>180</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C18" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E18" t="s">
         <v>270</v>
@@ -2834,197 +4213,197 @@
         <v>274</v>
       </c>
       <c r="C19" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E19" t="s">
         <v>275</v>
       </c>
-      <c r="D19" t="s">
-        <v>186</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>276</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>278</v>
+      </c>
+      <c r="B20" t="s">
         <v>279</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>233</v>
+      </c>
+      <c r="D20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" t="s">
         <v>280</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="D20" t="s">
-        <v>186</v>
-      </c>
-      <c r="E20" t="s">
-        <v>282</v>
-      </c>
-      <c r="F20" t="s">
-        <v>283</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" t="s">
+        <v>282</v>
+      </c>
+      <c r="C21" t="s">
+        <v>283</v>
+      </c>
+      <c r="D21" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" t="s">
+        <v>284</v>
+      </c>
+      <c r="F21" t="s">
         <v>285</v>
       </c>
-      <c r="B21" t="s">
+      <c r="H21" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="C21" t="s">
-        <v>192</v>
-      </c>
-      <c r="D21" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" t="s">
-        <v>287</v>
-      </c>
-      <c r="F21" t="s">
-        <v>288</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>287</v>
+      </c>
+      <c r="B22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C22" t="s">
+        <v>289</v>
+      </c>
+      <c r="D22" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" t="s">
         <v>290</v>
       </c>
-      <c r="B22" t="s">
+      <c r="F22" t="s">
         <v>291</v>
       </c>
-      <c r="C22" t="s">
-        <v>178</v>
-      </c>
-      <c r="D22" t="s">
-        <v>186</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="H22" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="F22" t="s">
-        <v>293</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>293</v>
+      </c>
+      <c r="B23" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" t="s">
+        <v>294</v>
+      </c>
+      <c r="F23" t="s">
         <v>295</v>
       </c>
-      <c r="B23" t="s">
+      <c r="H23" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="C23" t="s">
-        <v>226</v>
-      </c>
-      <c r="D23" t="s">
-        <v>186</v>
-      </c>
-      <c r="E23" t="s">
-        <v>297</v>
-      </c>
-      <c r="F23" t="s">
-        <v>298</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>297</v>
+      </c>
+      <c r="B24" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" t="s">
+        <v>299</v>
+      </c>
+      <c r="D24" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24" t="s">
         <v>300</v>
       </c>
-      <c r="B24" t="s">
+      <c r="F24" t="s">
         <v>301</v>
       </c>
-      <c r="C24" t="s">
+      <c r="H24" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="D24" t="s">
-        <v>251</v>
-      </c>
-      <c r="E24" t="s">
-        <v>303</v>
-      </c>
-      <c r="F24" t="s">
-        <v>304</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>303</v>
+      </c>
+      <c r="B25" t="s">
+        <v>304</v>
+      </c>
+      <c r="C25" t="s">
+        <v>305</v>
+      </c>
+      <c r="D25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E25" t="s">
         <v>306</v>
       </c>
-      <c r="B25" t="s">
+      <c r="F25" t="s">
         <v>307</v>
       </c>
-      <c r="C25" t="s">
+      <c r="H25" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="D25" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" t="s">
-        <v>309</v>
-      </c>
-      <c r="F25" t="s">
-        <v>310</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>309</v>
+      </c>
+      <c r="B26" t="s">
+        <v>310</v>
+      </c>
+      <c r="C26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D26" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" t="s">
         <v>312</v>
       </c>
-      <c r="B26" t="s">
+      <c r="F26" t="s">
         <v>313</v>
       </c>
-      <c r="C26" t="s">
-        <v>178</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="H26" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E26" t="s">
-        <v>264</v>
-      </c>
-      <c r="F26" t="s">
-        <v>315</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C27" t="s">
         <v>317</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" t="s">
         <v>318</v>
-      </c>
-      <c r="C27" t="s">
-        <v>220</v>
-      </c>
-      <c r="D27" t="s">
-        <v>193</v>
-      </c>
-      <c r="E27" t="s">
-        <v>264</v>
       </c>
       <c r="F27" t="s">
         <v>319</v>
@@ -3041,102 +4420,102 @@
         <v>322</v>
       </c>
       <c r="C28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D28" t="s">
         <v>323</v>
       </c>
-      <c r="D28" t="s">
-        <v>186</v>
-      </c>
       <c r="E28" t="s">
+        <v>180</v>
+      </c>
+      <c r="F28" t="s">
+        <v>307</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="F28" t="s">
-        <v>325</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>325</v>
+      </c>
+      <c r="B29" t="s">
+        <v>326</v>
+      </c>
+      <c r="C29" t="s">
         <v>327</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" t="s">
         <v>328</v>
       </c>
-      <c r="C29" t="s">
+      <c r="F29" t="s">
         <v>329</v>
       </c>
-      <c r="D29" t="s">
-        <v>186</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="H29" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="F29" t="s">
-        <v>331</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B30" t="s">
+        <v>332</v>
+      </c>
+      <c r="C30" t="s">
         <v>333</v>
       </c>
-      <c r="B30" t="s">
-        <v>268</v>
-      </c>
-      <c r="C30" t="s">
-        <v>269</v>
-      </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E30" t="s">
         <v>334</v>
       </c>
       <c r="F30" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B31" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C31" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D31" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E31" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F31" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C32" t="s">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="D32" t="s">
-        <v>251</v>
+        <v>190</v>
       </c>
       <c r="E32" t="s">
         <v>345</v>
@@ -3150,140 +4529,2279 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B33" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C33" t="s">
-        <v>348</v>
+        <v>185</v>
       </c>
       <c r="D33" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="E33" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F33" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B34" t="s">
-        <v>352</v>
+        <v>238</v>
       </c>
       <c r="C34" t="s">
+        <v>233</v>
+      </c>
+      <c r="D34" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34" t="s">
         <v>353</v>
       </c>
-      <c r="D34" t="s">
-        <v>186</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>240</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="F34" t="s">
-        <v>355</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>355</v>
+      </c>
+      <c r="B35" t="s">
+        <v>356</v>
+      </c>
+      <c r="C35" t="s">
         <v>357</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
+        <v>190</v>
+      </c>
+      <c r="E35" t="s">
         <v>358</v>
       </c>
-      <c r="C35" t="s">
+      <c r="F35" t="s">
         <v>359</v>
       </c>
-      <c r="D35" t="s">
-        <v>193</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="H35" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="F35" t="s">
-        <v>361</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>361</v>
+      </c>
+      <c r="B36" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" t="s">
+        <v>362</v>
+      </c>
+      <c r="D36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E36" t="s">
         <v>363</v>
       </c>
-      <c r="B36" t="s">
+      <c r="F36" t="s">
         <v>364</v>
       </c>
-      <c r="C36" t="s">
+      <c r="H36" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="D36" t="s">
-        <v>186</v>
-      </c>
-      <c r="E36" t="s">
-        <v>366</v>
-      </c>
-      <c r="F36" t="s">
-        <v>367</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>366</v>
+      </c>
+      <c r="B37" t="s">
+        <v>367</v>
+      </c>
+      <c r="C37" t="s">
+        <v>368</v>
+      </c>
+      <c r="D37" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" t="s">
         <v>369</v>
       </c>
-      <c r="B37" t="s">
+      <c r="F37" t="s">
         <v>370</v>
       </c>
-      <c r="C37" t="s">
-        <v>226</v>
-      </c>
-      <c r="D37" t="s">
-        <v>186</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="H37" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="F37" t="s">
-        <v>372</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>372</v>
+      </c>
+      <c r="B38" t="s">
+        <v>373</v>
+      </c>
+      <c r="C38" t="s">
+        <v>339</v>
+      </c>
+      <c r="D38" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" t="s">
         <v>374</v>
       </c>
-      <c r="B38" t="s">
-        <v>280</v>
-      </c>
-      <c r="C38" t="s">
-        <v>281</v>
-      </c>
-      <c r="D38" t="s">
-        <v>193</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>375</v>
-      </c>
-      <c r="F38" t="s">
-        <v>283</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>376</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>377</v>
+      </c>
+      <c r="B39" t="s">
+        <v>378</v>
+      </c>
+      <c r="C39" t="s">
+        <v>233</v>
+      </c>
+      <c r="D39" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" t="s">
+        <v>379</v>
+      </c>
+      <c r="F39" t="s">
+        <v>246</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>381</v>
+      </c>
+      <c r="B40" t="s">
+        <v>382</v>
+      </c>
+      <c r="C40" t="s">
+        <v>339</v>
+      </c>
+      <c r="D40" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" t="s">
+        <v>383</v>
+      </c>
+      <c r="F40" t="s">
+        <v>291</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>385</v>
+      </c>
+      <c r="B41" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41" t="s">
+        <v>196</v>
+      </c>
+      <c r="E41" t="s">
+        <v>197</v>
+      </c>
+      <c r="F41" t="s">
+        <v>198</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>387</v>
+      </c>
+      <c r="B42" t="s">
+        <v>388</v>
+      </c>
+      <c r="C42" t="s">
+        <v>185</v>
+      </c>
+      <c r="D42" t="s">
+        <v>190</v>
+      </c>
+      <c r="E42" t="s">
+        <v>389</v>
+      </c>
+      <c r="F42" t="s">
+        <v>390</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>392</v>
+      </c>
+      <c r="B43" t="s">
+        <v>393</v>
+      </c>
+      <c r="C43" t="s">
+        <v>394</v>
+      </c>
+      <c r="D43" t="s">
+        <v>190</v>
+      </c>
+      <c r="E43" t="s">
+        <v>395</v>
+      </c>
+      <c r="F43" t="s">
+        <v>396</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>398</v>
+      </c>
+      <c r="B44" t="s">
+        <v>399</v>
+      </c>
+      <c r="C44" t="s">
+        <v>400</v>
+      </c>
+      <c r="D44" t="s">
+        <v>190</v>
+      </c>
+      <c r="E44" t="s">
+        <v>401</v>
+      </c>
+      <c r="F44" t="s">
+        <v>402</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>404</v>
+      </c>
+      <c r="B45" t="s">
+        <v>405</v>
+      </c>
+      <c r="C45" t="s">
+        <v>368</v>
+      </c>
+      <c r="D45" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" t="s">
+        <v>406</v>
+      </c>
+      <c r="F45" t="s">
+        <v>407</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>409</v>
+      </c>
+      <c r="B46" t="s">
+        <v>410</v>
+      </c>
+      <c r="C46" t="s">
+        <v>411</v>
+      </c>
+      <c r="D46" t="s">
+        <v>190</v>
+      </c>
+      <c r="E46" t="s">
+        <v>412</v>
+      </c>
+      <c r="F46" t="s">
+        <v>413</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>415</v>
+      </c>
+      <c r="B47" t="s">
+        <v>416</v>
+      </c>
+      <c r="C47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D47" t="s">
+        <v>190</v>
+      </c>
+      <c r="E47" t="s">
+        <v>417</v>
+      </c>
+      <c r="F47" t="s">
+        <v>418</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>420</v>
+      </c>
+      <c r="B48" t="s">
+        <v>421</v>
+      </c>
+      <c r="C48" t="s">
+        <v>422</v>
+      </c>
+      <c r="D48" t="s">
+        <v>190</v>
+      </c>
+      <c r="E48" t="s">
+        <v>423</v>
+      </c>
+      <c r="F48" t="s">
+        <v>271</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>425</v>
+      </c>
+      <c r="B49" t="s">
+        <v>426</v>
+      </c>
+      <c r="C49" t="s">
+        <v>368</v>
+      </c>
+      <c r="D49" t="s">
+        <v>190</v>
+      </c>
+      <c r="E49" t="s">
+        <v>427</v>
+      </c>
+      <c r="F49" t="s">
+        <v>428</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>430</v>
+      </c>
+      <c r="B50" t="s">
+        <v>431</v>
+      </c>
+      <c r="C50" t="s">
+        <v>432</v>
+      </c>
+      <c r="D50" t="s">
+        <v>190</v>
+      </c>
+      <c r="E50" t="s">
+        <v>433</v>
+      </c>
+      <c r="F50" t="s">
+        <v>180</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B51" t="s">
+        <v>436</v>
+      </c>
+      <c r="C51" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" t="s">
+        <v>437</v>
+      </c>
+      <c r="F51" t="s">
+        <v>438</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>440</v>
+      </c>
+      <c r="B52" t="s">
+        <v>220</v>
+      </c>
+      <c r="C52" t="s">
+        <v>441</v>
+      </c>
+      <c r="D52" t="s">
+        <v>190</v>
+      </c>
+      <c r="E52" t="s">
+        <v>442</v>
+      </c>
+      <c r="F52" t="s">
+        <v>364</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>444</v>
+      </c>
+      <c r="B53" t="s">
+        <v>220</v>
+      </c>
+      <c r="C53" t="s">
+        <v>233</v>
+      </c>
+      <c r="D53" t="s">
+        <v>190</v>
+      </c>
+      <c r="E53" t="s">
+        <v>445</v>
+      </c>
+      <c r="F53" t="s">
+        <v>364</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>447</v>
+      </c>
+      <c r="B54" t="s">
+        <v>448</v>
+      </c>
+      <c r="C54" t="s">
+        <v>233</v>
+      </c>
+      <c r="D54" t="s">
+        <v>190</v>
+      </c>
+      <c r="E54" t="s">
+        <v>449</v>
+      </c>
+      <c r="F54" t="s">
+        <v>450</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>452</v>
+      </c>
+      <c r="B55" t="s">
+        <v>453</v>
+      </c>
+      <c r="C55" t="s">
+        <v>454</v>
+      </c>
+      <c r="D55" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" t="s">
+        <v>455</v>
+      </c>
+      <c r="F55" t="s">
+        <v>456</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>458</v>
+      </c>
+      <c r="B56" t="s">
+        <v>459</v>
+      </c>
+      <c r="C56" t="s">
+        <v>185</v>
+      </c>
+      <c r="D56" t="s">
+        <v>190</v>
+      </c>
+      <c r="E56" t="s">
+        <v>460</v>
+      </c>
+      <c r="F56" t="s">
+        <v>461</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>463</v>
+      </c>
+      <c r="B57" t="s">
+        <v>464</v>
+      </c>
+      <c r="C57" t="s">
+        <v>185</v>
+      </c>
+      <c r="D57" t="s">
+        <v>190</v>
+      </c>
+      <c r="E57" t="s">
+        <v>465</v>
+      </c>
+      <c r="F57" t="s">
+        <v>180</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>467</v>
+      </c>
+      <c r="B58" t="s">
+        <v>468</v>
+      </c>
+      <c r="C58" t="s">
+        <v>233</v>
+      </c>
+      <c r="D58" t="s">
+        <v>190</v>
+      </c>
+      <c r="E58" t="s">
+        <v>469</v>
+      </c>
+      <c r="F58" t="s">
+        <v>470</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>472</v>
+      </c>
+      <c r="B59" t="s">
+        <v>473</v>
+      </c>
+      <c r="C59" t="s">
+        <v>368</v>
+      </c>
+      <c r="D59" t="s">
+        <v>190</v>
+      </c>
+      <c r="E59" t="s">
+        <v>474</v>
+      </c>
+      <c r="F59" t="s">
+        <v>475</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>472</v>
+      </c>
+      <c r="B60" t="s">
+        <v>477</v>
+      </c>
+      <c r="C60" t="s">
+        <v>233</v>
+      </c>
+      <c r="D60" t="s">
+        <v>190</v>
+      </c>
+      <c r="E60" t="s">
+        <v>478</v>
+      </c>
+      <c r="F60" t="s">
+        <v>246</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>472</v>
+      </c>
+      <c r="B61" t="s">
+        <v>480</v>
+      </c>
+      <c r="C61" t="s">
+        <v>311</v>
+      </c>
+      <c r="D61" t="s">
+        <v>190</v>
+      </c>
+      <c r="E61" t="s">
+        <v>180</v>
+      </c>
+      <c r="F61" t="s">
+        <v>180</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>472</v>
+      </c>
+      <c r="B62" t="s">
+        <v>482</v>
+      </c>
+      <c r="C62" t="s">
+        <v>411</v>
+      </c>
+      <c r="D62" t="s">
+        <v>190</v>
+      </c>
+      <c r="E62" t="s">
+        <v>483</v>
+      </c>
+      <c r="F62" t="s">
+        <v>484</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>472</v>
+      </c>
+      <c r="B63" t="s">
+        <v>486</v>
+      </c>
+      <c r="C63" t="s">
+        <v>487</v>
+      </c>
+      <c r="D63" t="s">
+        <v>190</v>
+      </c>
+      <c r="E63" t="s">
+        <v>488</v>
+      </c>
+      <c r="F63" t="s">
+        <v>489</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>491</v>
+      </c>
+      <c r="B64" t="s">
+        <v>492</v>
+      </c>
+      <c r="C64" t="s">
+        <v>493</v>
+      </c>
+      <c r="D64" t="s">
+        <v>190</v>
+      </c>
+      <c r="E64" t="s">
+        <v>488</v>
+      </c>
+      <c r="F64" t="s">
+        <v>494</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>496</v>
+      </c>
+      <c r="B65" t="s">
+        <v>497</v>
+      </c>
+      <c r="C65" t="s">
+        <v>498</v>
+      </c>
+      <c r="D65" t="s">
+        <v>190</v>
+      </c>
+      <c r="E65" t="s">
+        <v>499</v>
+      </c>
+      <c r="F65" t="s">
+        <v>500</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>502</v>
+      </c>
+      <c r="B66" t="s">
+        <v>503</v>
+      </c>
+      <c r="C66" t="s">
+        <v>504</v>
+      </c>
+      <c r="D66" t="s">
+        <v>505</v>
+      </c>
+      <c r="E66" t="s">
+        <v>506</v>
+      </c>
+      <c r="F66" t="s">
+        <v>507</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>509</v>
+      </c>
+      <c r="B67" t="s">
+        <v>510</v>
+      </c>
+      <c r="C67" t="s">
+        <v>511</v>
+      </c>
+      <c r="D67" t="s">
+        <v>190</v>
+      </c>
+      <c r="E67" t="s">
+        <v>512</v>
+      </c>
+      <c r="F67" t="s">
+        <v>513</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>515</v>
+      </c>
+      <c r="B68" t="s">
+        <v>516</v>
+      </c>
+      <c r="C68" t="s">
+        <v>517</v>
+      </c>
+      <c r="D68" t="s">
+        <v>190</v>
+      </c>
+      <c r="E68" t="s">
+        <v>518</v>
+      </c>
+      <c r="F68" t="s">
+        <v>519</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>521</v>
+      </c>
+      <c r="B69" t="s">
+        <v>522</v>
+      </c>
+      <c r="C69" t="s">
+        <v>523</v>
+      </c>
+      <c r="D69" t="s">
+        <v>203</v>
+      </c>
+      <c r="E69" t="s">
+        <v>524</v>
+      </c>
+      <c r="F69" t="s">
+        <v>525</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>527</v>
+      </c>
+      <c r="B70" t="s">
+        <v>528</v>
+      </c>
+      <c r="C70" t="s">
+        <v>305</v>
+      </c>
+      <c r="D70" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" t="s">
+        <v>529</v>
+      </c>
+      <c r="F70" t="s">
+        <v>530</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>532</v>
+      </c>
+      <c r="B71" t="s">
+        <v>220</v>
+      </c>
+      <c r="C71" t="s">
+        <v>185</v>
+      </c>
+      <c r="D71" t="s">
+        <v>190</v>
+      </c>
+      <c r="E71" t="s">
+        <v>533</v>
+      </c>
+      <c r="F71" t="s">
+        <v>364</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>535</v>
+      </c>
+      <c r="B72" t="s">
+        <v>220</v>
+      </c>
+      <c r="C72" t="s">
+        <v>185</v>
+      </c>
+      <c r="D72" t="s">
+        <v>196</v>
+      </c>
+      <c r="E72" t="s">
+        <v>536</v>
+      </c>
+      <c r="F72" t="s">
+        <v>295</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>538</v>
+      </c>
+      <c r="B73" t="s">
+        <v>539</v>
+      </c>
+      <c r="C73" t="s">
+        <v>540</v>
+      </c>
+      <c r="D73" t="s">
+        <v>190</v>
+      </c>
+      <c r="E73" t="s">
+        <v>541</v>
+      </c>
+      <c r="F73" t="s">
+        <v>542</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>544</v>
+      </c>
+      <c r="B74" t="s">
+        <v>316</v>
+      </c>
+      <c r="C74" t="s">
+        <v>317</v>
+      </c>
+      <c r="D74" t="s">
+        <v>190</v>
+      </c>
+      <c r="E74" t="s">
+        <v>545</v>
+      </c>
+      <c r="F74" t="s">
+        <v>546</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>548</v>
+      </c>
+      <c r="B75" t="s">
+        <v>549</v>
+      </c>
+      <c r="C75" t="s">
+        <v>550</v>
+      </c>
+      <c r="D75" t="s">
+        <v>196</v>
+      </c>
+      <c r="E75" t="s">
+        <v>551</v>
+      </c>
+      <c r="F75" t="s">
+        <v>552</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>554</v>
+      </c>
+      <c r="B76" t="s">
+        <v>555</v>
+      </c>
+      <c r="C76" t="s">
+        <v>357</v>
+      </c>
+      <c r="D76" t="s">
+        <v>190</v>
+      </c>
+      <c r="E76" t="s">
+        <v>222</v>
+      </c>
+      <c r="F76" t="s">
+        <v>556</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>558</v>
+      </c>
+      <c r="B77" t="s">
+        <v>367</v>
+      </c>
+      <c r="C77" t="s">
+        <v>368</v>
+      </c>
+      <c r="D77" t="s">
+        <v>505</v>
+      </c>
+      <c r="E77" t="s">
+        <v>559</v>
+      </c>
+      <c r="F77" t="s">
+        <v>560</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>562</v>
+      </c>
+      <c r="B78" t="s">
+        <v>563</v>
+      </c>
+      <c r="C78" t="s">
+        <v>339</v>
+      </c>
+      <c r="D78" t="s">
+        <v>323</v>
+      </c>
+      <c r="E78" t="s">
+        <v>564</v>
+      </c>
+      <c r="F78" t="s">
+        <v>565</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>567</v>
+      </c>
+      <c r="B79" t="s">
+        <v>568</v>
+      </c>
+      <c r="C79" t="s">
+        <v>569</v>
+      </c>
+      <c r="D79" t="s">
+        <v>190</v>
+      </c>
+      <c r="E79" t="s">
+        <v>570</v>
+      </c>
+      <c r="F79" t="s">
+        <v>571</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>573</v>
+      </c>
+      <c r="B80" t="s">
+        <v>574</v>
+      </c>
+      <c r="C80" t="s">
+        <v>575</v>
+      </c>
+      <c r="D80" t="s">
+        <v>190</v>
+      </c>
+      <c r="E80" t="s">
+        <v>576</v>
+      </c>
+      <c r="F80" t="s">
+        <v>577</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>579</v>
+      </c>
+      <c r="B81" t="s">
+        <v>580</v>
+      </c>
+      <c r="C81" t="s">
+        <v>244</v>
+      </c>
+      <c r="D81" t="s">
+        <v>190</v>
+      </c>
+      <c r="E81" t="s">
+        <v>228</v>
+      </c>
+      <c r="F81" t="s">
+        <v>581</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>583</v>
+      </c>
+      <c r="B82" t="s">
+        <v>584</v>
+      </c>
+      <c r="C82" t="s">
+        <v>185</v>
+      </c>
+      <c r="D82" t="s">
+        <v>190</v>
+      </c>
+      <c r="E82" t="s">
+        <v>417</v>
+      </c>
+      <c r="F82" t="s">
+        <v>319</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>586</v>
+      </c>
+      <c r="B83" t="s">
+        <v>587</v>
+      </c>
+      <c r="C83" t="s">
+        <v>233</v>
+      </c>
+      <c r="D83" t="s">
+        <v>190</v>
+      </c>
+      <c r="E83" t="s">
+        <v>588</v>
+      </c>
+      <c r="F83" t="s">
+        <v>589</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>591</v>
+      </c>
+      <c r="B84" t="s">
+        <v>592</v>
+      </c>
+      <c r="C84" t="s">
+        <v>368</v>
+      </c>
+      <c r="D84" t="s">
+        <v>190</v>
+      </c>
+      <c r="E84" t="s">
+        <v>593</v>
+      </c>
+      <c r="F84" t="s">
+        <v>594</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>596</v>
+      </c>
+      <c r="B85" t="s">
+        <v>597</v>
+      </c>
+      <c r="C85" t="s">
+        <v>185</v>
+      </c>
+      <c r="D85" t="s">
+        <v>190</v>
+      </c>
+      <c r="E85" t="s">
+        <v>598</v>
+      </c>
+      <c r="F85" t="s">
+        <v>599</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>601</v>
+      </c>
+      <c r="B86" t="s">
+        <v>602</v>
+      </c>
+      <c r="C86" t="s">
+        <v>432</v>
+      </c>
+      <c r="D86" t="s">
+        <v>190</v>
+      </c>
+      <c r="E86" t="s">
+        <v>603</v>
+      </c>
+      <c r="F86" t="s">
+        <v>604</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>606</v>
+      </c>
+      <c r="B87" t="s">
+        <v>607</v>
+      </c>
+      <c r="C87" t="s">
+        <v>608</v>
+      </c>
+      <c r="D87" t="s">
+        <v>190</v>
+      </c>
+      <c r="E87" t="s">
+        <v>609</v>
+      </c>
+      <c r="F87" t="s">
+        <v>610</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>612</v>
+      </c>
+      <c r="B88" t="s">
+        <v>613</v>
+      </c>
+      <c r="C88" t="s">
+        <v>614</v>
+      </c>
+      <c r="D88" t="s">
+        <v>505</v>
+      </c>
+      <c r="E88" t="s">
+        <v>615</v>
+      </c>
+      <c r="F88" t="s">
+        <v>616</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>618</v>
+      </c>
+      <c r="B89" t="s">
+        <v>619</v>
+      </c>
+      <c r="C89" t="s">
+        <v>620</v>
+      </c>
+      <c r="D89" t="s">
+        <v>196</v>
+      </c>
+      <c r="E89" t="s">
+        <v>621</v>
+      </c>
+      <c r="F89" t="s">
+        <v>622</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>624</v>
+      </c>
+      <c r="B90" t="s">
+        <v>625</v>
+      </c>
+      <c r="C90" t="s">
+        <v>626</v>
+      </c>
+      <c r="D90" t="s">
+        <v>203</v>
+      </c>
+      <c r="E90" t="s">
+        <v>627</v>
+      </c>
+      <c r="F90" t="s">
+        <v>628</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>630</v>
+      </c>
+      <c r="B91" t="s">
+        <v>631</v>
+      </c>
+      <c r="C91" t="s">
+        <v>185</v>
+      </c>
+      <c r="D91" t="s">
+        <v>323</v>
+      </c>
+      <c r="E91" t="s">
+        <v>524</v>
+      </c>
+      <c r="F91" t="s">
+        <v>632</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>634</v>
+      </c>
+      <c r="B92" t="s">
+        <v>635</v>
+      </c>
+      <c r="C92" t="s">
+        <v>368</v>
+      </c>
+      <c r="D92" t="s">
+        <v>203</v>
+      </c>
+      <c r="E92" t="s">
+        <v>524</v>
+      </c>
+      <c r="F92" t="s">
+        <v>636</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>638</v>
+      </c>
+      <c r="B93" t="s">
+        <v>639</v>
+      </c>
+      <c r="C93" t="s">
+        <v>640</v>
+      </c>
+      <c r="D93" t="s">
+        <v>190</v>
+      </c>
+      <c r="E93" t="s">
+        <v>641</v>
+      </c>
+      <c r="F93" t="s">
+        <v>642</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>644</v>
+      </c>
+      <c r="B94" t="s">
+        <v>645</v>
+      </c>
+      <c r="C94" t="s">
+        <v>646</v>
+      </c>
+      <c r="D94" t="s">
+        <v>190</v>
+      </c>
+      <c r="E94" t="s">
+        <v>180</v>
+      </c>
+      <c r="F94" t="s">
+        <v>647</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>649</v>
+      </c>
+      <c r="B95" t="s">
+        <v>650</v>
+      </c>
+      <c r="C95" t="s">
+        <v>233</v>
+      </c>
+      <c r="D95" t="s">
+        <v>190</v>
+      </c>
+      <c r="E95" t="s">
+        <v>442</v>
+      </c>
+      <c r="F95" t="s">
+        <v>651</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>653</v>
+      </c>
+      <c r="B96" t="s">
+        <v>654</v>
+      </c>
+      <c r="C96" t="s">
+        <v>655</v>
+      </c>
+      <c r="D96" t="s">
+        <v>203</v>
+      </c>
+      <c r="E96" t="s">
+        <v>656</v>
+      </c>
+      <c r="F96" t="s">
+        <v>657</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>659</v>
+      </c>
+      <c r="B97" t="s">
+        <v>660</v>
+      </c>
+      <c r="C97" t="s">
+        <v>661</v>
+      </c>
+      <c r="D97" t="s">
+        <v>190</v>
+      </c>
+      <c r="E97" t="s">
+        <v>662</v>
+      </c>
+      <c r="F97" t="s">
+        <v>663</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>665</v>
+      </c>
+      <c r="B98" t="s">
+        <v>666</v>
+      </c>
+      <c r="C98" t="s">
+        <v>667</v>
+      </c>
+      <c r="D98" t="s">
+        <v>190</v>
+      </c>
+      <c r="E98" t="s">
+        <v>668</v>
+      </c>
+      <c r="F98" t="s">
+        <v>246</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>670</v>
+      </c>
+      <c r="B99" t="s">
+        <v>671</v>
+      </c>
+      <c r="C99" t="s">
+        <v>672</v>
+      </c>
+      <c r="D99" t="s">
+        <v>190</v>
+      </c>
+      <c r="E99" t="s">
+        <v>673</v>
+      </c>
+      <c r="F99" t="s">
+        <v>674</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>676</v>
+      </c>
+      <c r="B100" t="s">
+        <v>677</v>
+      </c>
+      <c r="C100" t="s">
+        <v>678</v>
+      </c>
+      <c r="D100" t="s">
+        <v>190</v>
+      </c>
+      <c r="E100" t="s">
+        <v>679</v>
+      </c>
+      <c r="F100" t="s">
+        <v>680</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>682</v>
+      </c>
+      <c r="B101" t="s">
+        <v>568</v>
+      </c>
+      <c r="C101" t="s">
+        <v>569</v>
+      </c>
+      <c r="D101" t="s">
+        <v>190</v>
+      </c>
+      <c r="E101" t="s">
+        <v>683</v>
+      </c>
+      <c r="F101" t="s">
+        <v>571</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>685</v>
+      </c>
+      <c r="B102" t="s">
+        <v>686</v>
+      </c>
+      <c r="C102" t="s">
+        <v>687</v>
+      </c>
+      <c r="D102" t="s">
+        <v>190</v>
+      </c>
+      <c r="E102" t="s">
+        <v>688</v>
+      </c>
+      <c r="F102" t="s">
+        <v>689</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>691</v>
+      </c>
+      <c r="B103" t="s">
+        <v>338</v>
+      </c>
+      <c r="C103" t="s">
+        <v>339</v>
+      </c>
+      <c r="D103" t="s">
+        <v>203</v>
+      </c>
+      <c r="E103" t="s">
+        <v>445</v>
+      </c>
+      <c r="F103" t="s">
+        <v>341</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>693</v>
+      </c>
+      <c r="B104" t="s">
+        <v>694</v>
+      </c>
+      <c r="C104" t="s">
+        <v>695</v>
+      </c>
+      <c r="D104" t="s">
+        <v>505</v>
+      </c>
+      <c r="E104" t="s">
+        <v>696</v>
+      </c>
+      <c r="F104" t="s">
+        <v>697</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>693</v>
+      </c>
+      <c r="B105" t="s">
+        <v>694</v>
+      </c>
+      <c r="C105" t="s">
+        <v>699</v>
+      </c>
+      <c r="D105" t="s">
+        <v>505</v>
+      </c>
+      <c r="E105" t="s">
+        <v>696</v>
+      </c>
+      <c r="F105" t="s">
+        <v>700</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>702</v>
+      </c>
+      <c r="B106" t="s">
+        <v>703</v>
+      </c>
+      <c r="C106" t="s">
+        <v>411</v>
+      </c>
+      <c r="D106" t="s">
+        <v>190</v>
+      </c>
+      <c r="E106" t="s">
+        <v>536</v>
+      </c>
+      <c r="F106" t="s">
+        <v>704</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>706</v>
+      </c>
+      <c r="B107" t="s">
+        <v>707</v>
+      </c>
+      <c r="C107" t="s">
+        <v>185</v>
+      </c>
+      <c r="D107" t="s">
+        <v>190</v>
+      </c>
+      <c r="E107" t="s">
+        <v>708</v>
+      </c>
+      <c r="F107" t="s">
+        <v>709</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>711</v>
+      </c>
+      <c r="B108" t="s">
+        <v>712</v>
+      </c>
+      <c r="C108" t="s">
+        <v>411</v>
+      </c>
+      <c r="D108" t="s">
+        <v>190</v>
+      </c>
+      <c r="E108" t="s">
+        <v>713</v>
+      </c>
+      <c r="F108" t="s">
+        <v>714</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>716</v>
+      </c>
+      <c r="B109" t="s">
+        <v>717</v>
+      </c>
+      <c r="C109" t="s">
+        <v>368</v>
+      </c>
+      <c r="D109" t="s">
+        <v>190</v>
+      </c>
+      <c r="E109" t="s">
+        <v>718</v>
+      </c>
+      <c r="F109" t="s">
+        <v>180</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>720</v>
+      </c>
+      <c r="B110" t="s">
+        <v>220</v>
+      </c>
+      <c r="C110" t="s">
+        <v>721</v>
+      </c>
+      <c r="D110" t="s">
+        <v>190</v>
+      </c>
+      <c r="E110" t="s">
+        <v>722</v>
+      </c>
+      <c r="F110" t="s">
+        <v>364</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>724</v>
+      </c>
+      <c r="B111" t="s">
+        <v>310</v>
+      </c>
+      <c r="C111" t="s">
+        <v>311</v>
+      </c>
+      <c r="D111" t="s">
+        <v>190</v>
+      </c>
+      <c r="E111" t="s">
+        <v>725</v>
+      </c>
+      <c r="F111" t="s">
+        <v>726</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>728</v>
+      </c>
+      <c r="B112" t="s">
+        <v>729</v>
+      </c>
+      <c r="C112" t="s">
+        <v>730</v>
+      </c>
+      <c r="D112" t="s">
+        <v>190</v>
+      </c>
+      <c r="E112" t="s">
+        <v>731</v>
+      </c>
+      <c r="F112" t="s">
+        <v>622</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>733</v>
+      </c>
+      <c r="B113" t="s">
+        <v>734</v>
+      </c>
+      <c r="C113" t="s">
+        <v>185</v>
+      </c>
+      <c r="D113" t="s">
+        <v>190</v>
+      </c>
+      <c r="E113" t="s">
+        <v>735</v>
+      </c>
+      <c r="F113" t="s">
+        <v>736</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>738</v>
+      </c>
+      <c r="B114" t="s">
+        <v>739</v>
+      </c>
+      <c r="C114" t="s">
+        <v>740</v>
+      </c>
+      <c r="D114" t="s">
+        <v>203</v>
+      </c>
+      <c r="E114" t="s">
+        <v>741</v>
+      </c>
+      <c r="F114" t="s">
+        <v>742</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>738</v>
+      </c>
+      <c r="B115" t="s">
+        <v>739</v>
+      </c>
+      <c r="C115" t="s">
+        <v>744</v>
+      </c>
+      <c r="D115" t="s">
+        <v>190</v>
+      </c>
+      <c r="E115" t="s">
+        <v>741</v>
+      </c>
+      <c r="F115" t="s">
+        <v>742</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>746</v>
+      </c>
+      <c r="B116" t="s">
+        <v>747</v>
+      </c>
+      <c r="C116" t="s">
+        <v>748</v>
+      </c>
+      <c r="D116" t="s">
+        <v>203</v>
+      </c>
+      <c r="E116" t="s">
+        <v>749</v>
+      </c>
+      <c r="F116" t="s">
+        <v>750</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>752</v>
+      </c>
+      <c r="B117" t="s">
+        <v>753</v>
+      </c>
+      <c r="C117" t="s">
+        <v>754</v>
+      </c>
+      <c r="D117" t="s">
+        <v>203</v>
+      </c>
+      <c r="E117" t="s">
+        <v>755</v>
+      </c>
+      <c r="F117" t="s">
+        <v>756</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>758</v>
+      </c>
+      <c r="B118" t="s">
+        <v>759</v>
+      </c>
+      <c r="C118" t="s">
+        <v>760</v>
+      </c>
+      <c r="D118" t="s">
+        <v>505</v>
+      </c>
+      <c r="E118" t="s">
+        <v>449</v>
+      </c>
+      <c r="F118" t="s">
+        <v>319</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>762</v>
+      </c>
+      <c r="B119" t="s">
+        <v>763</v>
+      </c>
+      <c r="C119" t="s">
+        <v>764</v>
+      </c>
+      <c r="D119" t="s">
+        <v>190</v>
+      </c>
+      <c r="E119" t="s">
+        <v>765</v>
+      </c>
+      <c r="F119" t="s">
+        <v>766</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>768</v>
+      </c>
+      <c r="B120" t="s">
+        <v>769</v>
+      </c>
+      <c r="C120" t="s">
+        <v>233</v>
+      </c>
+      <c r="D120" t="s">
+        <v>190</v>
+      </c>
+      <c r="E120" t="s">
+        <v>770</v>
+      </c>
+      <c r="F120" t="s">
+        <v>771</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>773</v>
+      </c>
+      <c r="B121" t="s">
+        <v>774</v>
+      </c>
+      <c r="C121" t="s">
+        <v>775</v>
+      </c>
+      <c r="D121" t="s">
+        <v>190</v>
+      </c>
+      <c r="E121" t="s">
+        <v>776</v>
+      </c>
+      <c r="F121" t="s">
+        <v>180</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>778</v>
+      </c>
+      <c r="B122" t="s">
+        <v>774</v>
+      </c>
+      <c r="C122" t="s">
+        <v>775</v>
+      </c>
+      <c r="D122" t="s">
+        <v>190</v>
+      </c>
+      <c r="E122" t="s">
+        <v>779</v>
+      </c>
+      <c r="F122" t="s">
+        <v>180</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>781</v>
+      </c>
+      <c r="B123" t="s">
+        <v>782</v>
+      </c>
+      <c r="C123" t="s">
+        <v>432</v>
+      </c>
+      <c r="D123" t="s">
+        <v>190</v>
+      </c>
+      <c r="E123" t="s">
+        <v>783</v>
+      </c>
+      <c r="F123" t="s">
+        <v>784</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>786</v>
+      </c>
+      <c r="B124" t="s">
+        <v>787</v>
+      </c>
+      <c r="C124" t="s">
+        <v>357</v>
+      </c>
+      <c r="D124" t="s">
+        <v>323</v>
+      </c>
+      <c r="E124" t="s">
+        <v>788</v>
+      </c>
+      <c r="F124" t="s">
+        <v>307</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>790</v>
+      </c>
+      <c r="B125" t="s">
+        <v>791</v>
+      </c>
+      <c r="C125" t="s">
+        <v>792</v>
+      </c>
+      <c r="D125" t="s">
+        <v>190</v>
+      </c>
+      <c r="E125" t="s">
+        <v>793</v>
+      </c>
+      <c r="F125" t="s">
+        <v>794</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>796</v>
+      </c>
+      <c r="B126" t="s">
+        <v>797</v>
+      </c>
+      <c r="C126" t="s">
+        <v>798</v>
+      </c>
+      <c r="D126" t="s">
+        <v>190</v>
+      </c>
+      <c r="E126" t="s">
+        <v>799</v>
+      </c>
+      <c r="F126" t="s">
+        <v>800</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>802</v>
+      </c>
+      <c r="B127" t="s">
+        <v>803</v>
+      </c>
+      <c r="C127" t="s">
+        <v>804</v>
+      </c>
+      <c r="D127" t="s">
+        <v>190</v>
+      </c>
+      <c r="E127" t="s">
+        <v>805</v>
+      </c>
+      <c r="F127" t="s">
+        <v>180</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>802</v>
+      </c>
+      <c r="B128" t="s">
+        <v>803</v>
+      </c>
+      <c r="C128" t="s">
+        <v>807</v>
+      </c>
+      <c r="D128" t="s">
+        <v>190</v>
+      </c>
+      <c r="E128" t="s">
+        <v>805</v>
+      </c>
+      <c r="F128" t="s">
+        <v>180</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>809</v>
+      </c>
+      <c r="B129" t="s">
+        <v>194</v>
+      </c>
+      <c r="C129" t="s">
+        <v>195</v>
+      </c>
+      <c r="D129" t="s">
+        <v>196</v>
+      </c>
+      <c r="E129" t="s">
+        <v>197</v>
+      </c>
+      <c r="F129" t="s">
+        <v>198</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>811</v>
+      </c>
+      <c r="B130" t="s">
+        <v>812</v>
+      </c>
+      <c r="C130" t="s">
+        <v>813</v>
+      </c>
+      <c r="D130" t="s">
+        <v>190</v>
+      </c>
+      <c r="E130" t="s">
+        <v>814</v>
+      </c>
+      <c r="F130" t="s">
+        <v>815</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>817</v>
+      </c>
+      <c r="B131" t="s">
+        <v>580</v>
+      </c>
+      <c r="C131" t="s">
+        <v>244</v>
+      </c>
+      <c r="D131" t="s">
+        <v>203</v>
+      </c>
+      <c r="E131" t="s">
+        <v>818</v>
+      </c>
+      <c r="F131" t="s">
+        <v>581</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>819</v>
       </c>
     </row>
   </sheetData>
@@ -3326,6 +6844,99 @@
     <hyperlink ref="H36" r:id="rId35"/>
     <hyperlink ref="H37" r:id="rId36"/>
     <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-24.xlsx
+++ b/docs/xlsx/jobs-2026-08-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="854">
   <si>
     <t>Title</t>
   </si>
@@ -544,6 +544,27 @@
     <t>https://www.conservationjobboard.com/job-listing-voter-registration-field-organizer-madison-wisconsin/1473533370</t>
   </si>
   <si>
+    <t>Business Engagement Manager, Corporate Standards</t>
+  </si>
+  <si>
+    <t>Action Speaks Louder</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Contractor</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Climate Change</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/business-engagement-manager-corporate-standards/</t>
+  </si>
+  <si>
     <t>Climate Change: Cap-and-Invest Senior Market Monitor (Financial Examiner 4)</t>
   </si>
   <si>
@@ -556,9 +577,6 @@
     <t>Full-Time</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Environmental</t>
   </si>
   <si>
@@ -571,9 +589,6 @@
     <t>Greenlight America</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Clean Energy</t>
   </si>
   <si>
@@ -805,6 +820,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/afb1169440aa444686c7332cd653f5dd-attendance-success-coordinator-elementary-zone-126-queens-county</t>
   </si>
   <si>
+    <t>Actions Speak Louder (ASL)</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b9efb6b5b37430d9f571242469e66a7-business-engagement-manager-corporate-standards-actions-speak-louder-asl-newcastle</t>
+  </si>
+  <si>
+    <t>Business Operations Manager</t>
+  </si>
+  <si>
+    <t>Veggielution</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 77126.00 - 77126.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Agriculture, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa35ed3b70144df7a17caac6ffb276ef-business-operations-manager-veggielution-san-jose</t>
+  </si>
+  <si>
     <t>Business Training Manager - Waltham</t>
   </si>
   <si>
@@ -979,6 +1021,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/4d3914b0230944c7a628700a9eed5ebe-corporate-relations-manager-fish-wildlife-foundation-of-florida-inc-tallahassee</t>
   </si>
   <si>
+    <t>Cultural Center Design &amp; Implementation Contractor</t>
+  </si>
+  <si>
+    <t>Refugee Artisan Initiative</t>
+  </si>
+  <si>
+    <t>USD 125.00 - 125.00/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/464e5bcde9b64119903dc7b6754d3d72-cultural-center-design-implementation-contractor-refugee-artisan-initiative-seattle</t>
+  </si>
+  <si>
     <t>Data Science Program Assistant/College Assistant</t>
   </si>
   <si>
@@ -1045,6 +1102,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/fe531380ec1d4a8bb568a7cedd206a82-deputy-director-sf-new-deal-san-francisco</t>
   </si>
   <si>
+    <t>Deputy Director of Legal Services</t>
+  </si>
+  <si>
+    <t>Legal Action Center (NYC, D.C.)</t>
+  </si>
+  <si>
+    <t>USD 115000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d114d41216f4cb0b9f37e204e676ca7-deputy-director-of-legal-services-legal-action-center-nyc-dc-new-york</t>
+  </si>
+  <si>
+    <t>Deputy Director of Litigation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54227fd814d74a0c89b56f1a7d308867-deputy-director-of-litigation-legal-action-center-nyc-dc-new-york</t>
+  </si>
+  <si>
     <t>Development &amp; Administrative Associate</t>
   </si>
   <si>
@@ -2071,6 +2149,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/27aa29b208784d54a4938f269e916c7e-program-lead-women-agency-mumbai-ground-zero-mumbai</t>
   </si>
   <si>
+    <t>Programme Manager - Community Health</t>
+  </si>
+  <si>
+    <t>SEED Madagascar</t>
+  </si>
+  <si>
+    <t>Taolagnaro, Anosy, MG</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3343ff025bd64b58aa69f3a959f75fc6-programme-manager-community-health-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Programs Coordinator, Fiscal Systems</t>
   </si>
   <si>
@@ -2288,6 +2381,15 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/28ff47bb64794ecf9e5e762d1e1bc6f0-special-collections-librarian-fairfield-museum-and-history-center-fairfield</t>
+  </si>
+  <si>
+    <t>Sr. Vice President of Legal Advocacy</t>
+  </si>
+  <si>
+    <t>USD 175000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7066b0d862a4b4e925ce7fc0b79f9d1-sr-vice-president-of-legal-advocacy-legal-action-center-nyc-dc-new-york</t>
   </si>
   <si>
     <t>Sr. Workplace Support Specialist (2-year term)</t>
@@ -3677,7 +3779,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3750,16 +3852,39 @@
         <v>185</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="E3" t="s">
         <v>180</v>
       </c>
       <c r="F3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" t="s">
         <v>186</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>187</v>
+      <c r="E4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -3767,6 +3892,7 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3775,7 +3901,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3816,292 +3942,292 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F2" t="s">
         <v>180</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F4" t="s">
         <v>180</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C7" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F7" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C8" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D8" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C9" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D9" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E9" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B10" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C10" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D10" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E10" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F10" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" t="s">
         <v>238</v>
       </c>
-      <c r="C11" t="s">
-        <v>233</v>
-      </c>
       <c r="D11" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E11" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F11" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E12" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F12" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B13" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C13" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E13" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F13" t="s">
         <v>180</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
         <v>180</v>
@@ -4110,579 +4236,579 @@
         <v>180</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B15" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F15" t="s">
         <v>180</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B16" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C16" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E16" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F16" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>263</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C17" t="s">
-        <v>265</v>
+        <v>178</v>
       </c>
       <c r="D17" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E17" t="s">
-        <v>266</v>
+        <v>180</v>
       </c>
       <c r="F17" t="s">
-        <v>180</v>
+        <v>269</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B18" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C18" t="s">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F18" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C19" t="s">
-        <v>185</v>
+        <v>279</v>
       </c>
       <c r="D19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>276</v>
+        <v>180</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B20" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C20" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D20" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E20" t="s">
-        <v>180</v>
+        <v>284</v>
       </c>
       <c r="F20" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>176</v>
+        <v>287</v>
       </c>
       <c r="B21" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C21" t="s">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="D21" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E21" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F21" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B22" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C22" t="s">
-        <v>289</v>
+        <v>238</v>
       </c>
       <c r="D22" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E22" t="s">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="F22" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>293</v>
+        <v>183</v>
       </c>
       <c r="B23" t="s">
-        <v>220</v>
+        <v>296</v>
       </c>
       <c r="C23" t="s">
-        <v>185</v>
+        <v>297</v>
       </c>
       <c r="D23" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E23" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F23" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C24" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D24" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E24" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F24" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B25" t="s">
-        <v>304</v>
+        <v>225</v>
       </c>
       <c r="C25" t="s">
-        <v>305</v>
+        <v>178</v>
       </c>
       <c r="D25" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E25" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F25" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C26" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D26" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E26" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F26" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B27" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C27" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D27" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E27" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F27" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B28" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C28" t="s">
-        <v>233</v>
+        <v>325</v>
       </c>
       <c r="D28" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E28" t="s">
-        <v>180</v>
+        <v>326</v>
       </c>
       <c r="F28" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B29" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C29" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D29" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E29" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F29" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B30" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C30" t="s">
-        <v>333</v>
+        <v>207</v>
       </c>
       <c r="D30" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E30" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F30" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C31" t="s">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="D31" t="s">
-        <v>190</v>
+        <v>342</v>
       </c>
       <c r="E31" t="s">
-        <v>340</v>
+        <v>180</v>
       </c>
       <c r="F31" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C32" t="s">
-        <v>233</v>
+        <v>346</v>
       </c>
       <c r="D32" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E32" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F32" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>185</v>
+        <v>352</v>
       </c>
       <c r="D33" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F33" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B34" t="s">
-        <v>238</v>
+        <v>357</v>
       </c>
       <c r="C34" t="s">
-        <v>233</v>
+        <v>358</v>
       </c>
       <c r="D34" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E34" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F34" t="s">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B35" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C35" t="s">
-        <v>357</v>
+        <v>238</v>
       </c>
       <c r="D35" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E35" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F35" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>363</v>
       </c>
       <c r="C36" t="s">
-        <v>362</v>
+        <v>238</v>
       </c>
       <c r="D36" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E36" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F36" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B37" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C37" t="s">
-        <v>368</v>
+        <v>238</v>
       </c>
       <c r="D37" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E37" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F37" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B38" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C38" t="s">
-        <v>339</v>
+        <v>178</v>
       </c>
       <c r="D38" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E38" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F38" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s">
-        <v>378</v>
+        <v>243</v>
       </c>
       <c r="C39" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D39" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E39" t="s">
         <v>379</v>
       </c>
       <c r="F39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>380</v>
@@ -4696,217 +4822,217 @@
         <v>382</v>
       </c>
       <c r="C40" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="D40" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E40" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F40" t="s">
-        <v>291</v>
+        <v>385</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B41" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="C41" t="s">
-        <v>195</v>
+        <v>388</v>
       </c>
       <c r="D41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E41" t="s">
-        <v>197</v>
+        <v>389</v>
       </c>
       <c r="F41" t="s">
-        <v>198</v>
+        <v>390</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>394</v>
       </c>
       <c r="D42" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E42" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="F42" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B43" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C43" t="s">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="D43" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E43" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F43" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B44" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C44" t="s">
-        <v>400</v>
+        <v>238</v>
       </c>
       <c r="D44" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E44" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F44" t="s">
-        <v>402</v>
+        <v>251</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C45" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D45" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E45" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F45" t="s">
-        <v>407</v>
+        <v>305</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B46" t="s">
-        <v>410</v>
+        <v>199</v>
       </c>
       <c r="C46" t="s">
-        <v>411</v>
+        <v>200</v>
       </c>
       <c r="D46" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E46" t="s">
+        <v>202</v>
+      </c>
+      <c r="F46" t="s">
+        <v>203</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="F46" t="s">
-        <v>413</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>413</v>
+      </c>
+      <c r="B47" t="s">
+        <v>414</v>
+      </c>
+      <c r="C47" t="s">
+        <v>178</v>
+      </c>
+      <c r="D47" t="s">
+        <v>195</v>
+      </c>
+      <c r="E47" t="s">
         <v>415</v>
       </c>
-      <c r="B47" t="s">
+      <c r="F47" t="s">
         <v>416</v>
       </c>
-      <c r="C47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D47" t="s">
-        <v>190</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="H47" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="F47" t="s">
-        <v>418</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>418</v>
+      </c>
+      <c r="B48" t="s">
+        <v>419</v>
+      </c>
+      <c r="C48" t="s">
         <v>420</v>
       </c>
-      <c r="B48" t="s">
+      <c r="D48" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" t="s">
         <v>421</v>
       </c>
-      <c r="C48" t="s">
+      <c r="F48" t="s">
         <v>422</v>
       </c>
-      <c r="D48" t="s">
-        <v>190</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="H48" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="F48" t="s">
-        <v>271</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>424</v>
+      </c>
+      <c r="B49" t="s">
         <v>425</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>426</v>
       </c>
-      <c r="C49" t="s">
-        <v>368</v>
-      </c>
       <c r="D49" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E49" t="s">
         <v>427</v>
@@ -4926,16 +5052,16 @@
         <v>431</v>
       </c>
       <c r="C50" t="s">
+        <v>394</v>
+      </c>
+      <c r="D50" t="s">
+        <v>195</v>
+      </c>
+      <c r="E50" t="s">
         <v>432</v>
       </c>
-      <c r="D50" t="s">
-        <v>190</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>433</v>
-      </c>
-      <c r="F50" t="s">
-        <v>180</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>434</v>
@@ -4949,476 +5075,476 @@
         <v>436</v>
       </c>
       <c r="C51" t="s">
-        <v>185</v>
+        <v>437</v>
       </c>
       <c r="D51" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E51" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F51" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B52" t="s">
-        <v>220</v>
+        <v>442</v>
       </c>
       <c r="C52" t="s">
-        <v>441</v>
+        <v>238</v>
       </c>
       <c r="D52" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E52" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F52" t="s">
-        <v>364</v>
+        <v>444</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B53" t="s">
-        <v>220</v>
+        <v>447</v>
       </c>
       <c r="C53" t="s">
-        <v>233</v>
+        <v>448</v>
       </c>
       <c r="D53" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E53" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F53" t="s">
-        <v>364</v>
+        <v>285</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B54" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C54" t="s">
-        <v>233</v>
+        <v>394</v>
       </c>
       <c r="D54" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E54" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F54" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B55" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C55" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D55" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E55" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F55" t="s">
-        <v>456</v>
+        <v>180</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B56" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C56" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D56" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E56" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F56" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B57" t="s">
-        <v>464</v>
+        <v>225</v>
       </c>
       <c r="C57" t="s">
-        <v>185</v>
+        <v>467</v>
       </c>
       <c r="D57" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E57" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F57" t="s">
-        <v>180</v>
+        <v>390</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B58" t="s">
-        <v>468</v>
+        <v>225</v>
       </c>
       <c r="C58" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D58" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E58" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F58" t="s">
-        <v>470</v>
+        <v>390</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C59" t="s">
-        <v>368</v>
+        <v>238</v>
       </c>
       <c r="D59" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E59" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F59" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C60" t="s">
-        <v>233</v>
+        <v>480</v>
       </c>
       <c r="D60" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E60" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F60" t="s">
-        <v>246</v>
+        <v>482</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="B61" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C61" t="s">
-        <v>311</v>
+        <v>178</v>
       </c>
       <c r="D61" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E61" t="s">
-        <v>180</v>
+        <v>486</v>
       </c>
       <c r="F61" t="s">
-        <v>180</v>
+        <v>487</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C62" t="s">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="D62" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E62" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F62" t="s">
-        <v>484</v>
+        <v>180</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="B63" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C63" t="s">
-        <v>487</v>
+        <v>238</v>
       </c>
       <c r="D63" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E63" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F63" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B64" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C64" t="s">
-        <v>493</v>
+        <v>394</v>
       </c>
       <c r="D64" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E64" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="F64" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B65" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C65" t="s">
-        <v>498</v>
+        <v>238</v>
       </c>
       <c r="D65" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E65" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F65" t="s">
-        <v>500</v>
+        <v>251</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C66" t="s">
-        <v>504</v>
+        <v>325</v>
       </c>
       <c r="D66" t="s">
-        <v>505</v>
+        <v>195</v>
       </c>
       <c r="E66" t="s">
-        <v>506</v>
+        <v>180</v>
       </c>
       <c r="F66" t="s">
+        <v>180</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>498</v>
+      </c>
+      <c r="B67" t="s">
+        <v>508</v>
+      </c>
+      <c r="C67" t="s">
+        <v>437</v>
+      </c>
+      <c r="D67" t="s">
+        <v>195</v>
+      </c>
+      <c r="E67" t="s">
         <v>509</v>
       </c>
-      <c r="B67" t="s">
+      <c r="F67" t="s">
         <v>510</v>
       </c>
-      <c r="C67" t="s">
+      <c r="H67" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="D67" t="s">
-        <v>190</v>
-      </c>
-      <c r="E67" t="s">
-        <v>512</v>
-      </c>
-      <c r="F67" t="s">
-        <v>513</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>498</v>
+      </c>
+      <c r="B68" t="s">
+        <v>512</v>
+      </c>
+      <c r="C68" t="s">
+        <v>513</v>
+      </c>
+      <c r="D68" t="s">
+        <v>195</v>
+      </c>
+      <c r="E68" t="s">
+        <v>514</v>
+      </c>
+      <c r="F68" t="s">
         <v>515</v>
       </c>
-      <c r="B68" t="s">
+      <c r="H68" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="C68" t="s">
-        <v>517</v>
-      </c>
-      <c r="D68" t="s">
-        <v>190</v>
-      </c>
-      <c r="E68" t="s">
-        <v>518</v>
-      </c>
-      <c r="F68" t="s">
-        <v>519</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>517</v>
+      </c>
+      <c r="B69" t="s">
+        <v>518</v>
+      </c>
+      <c r="C69" t="s">
+        <v>519</v>
+      </c>
+      <c r="D69" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" t="s">
+        <v>514</v>
+      </c>
+      <c r="F69" t="s">
+        <v>520</v>
+      </c>
+      <c r="H69" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="B69" t="s">
-        <v>522</v>
-      </c>
-      <c r="C69" t="s">
-        <v>523</v>
-      </c>
-      <c r="D69" t="s">
-        <v>203</v>
-      </c>
-      <c r="E69" t="s">
-        <v>524</v>
-      </c>
-      <c r="F69" t="s">
-        <v>525</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>522</v>
+      </c>
+      <c r="B70" t="s">
+        <v>523</v>
+      </c>
+      <c r="C70" t="s">
+        <v>524</v>
+      </c>
+      <c r="D70" t="s">
+        <v>195</v>
+      </c>
+      <c r="E70" t="s">
+        <v>525</v>
+      </c>
+      <c r="F70" t="s">
+        <v>526</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="B70" t="s">
-        <v>528</v>
-      </c>
-      <c r="C70" t="s">
-        <v>305</v>
-      </c>
-      <c r="D70" t="s">
-        <v>190</v>
-      </c>
-      <c r="E70" t="s">
-        <v>529</v>
-      </c>
-      <c r="F70" t="s">
-        <v>530</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>528</v>
+      </c>
+      <c r="B71" t="s">
+        <v>529</v>
+      </c>
+      <c r="C71" t="s">
+        <v>530</v>
+      </c>
+      <c r="D71" t="s">
+        <v>531</v>
+      </c>
+      <c r="E71" t="s">
         <v>532</v>
       </c>
-      <c r="B71" t="s">
-        <v>220</v>
-      </c>
-      <c r="C71" t="s">
-        <v>185</v>
-      </c>
-      <c r="D71" t="s">
-        <v>190</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>533</v>
-      </c>
-      <c r="F71" t="s">
-        <v>364</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>534</v>
@@ -5429,364 +5555,364 @@
         <v>535</v>
       </c>
       <c r="B72" t="s">
-        <v>220</v>
+        <v>536</v>
       </c>
       <c r="C72" t="s">
-        <v>185</v>
+        <v>537</v>
       </c>
       <c r="D72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E72" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F72" t="s">
-        <v>295</v>
+        <v>539</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B73" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C73" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D73" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E73" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F73" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B74" t="s">
-        <v>316</v>
+        <v>548</v>
       </c>
       <c r="C74" t="s">
-        <v>317</v>
+        <v>549</v>
       </c>
       <c r="D74" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E74" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="F74" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B75" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C75" t="s">
-        <v>550</v>
+        <v>319</v>
       </c>
       <c r="D75" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E75" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F75" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B76" t="s">
-        <v>555</v>
+        <v>225</v>
       </c>
       <c r="C76" t="s">
-        <v>357</v>
+        <v>178</v>
       </c>
       <c r="D76" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E76" t="s">
-        <v>222</v>
+        <v>559</v>
       </c>
       <c r="F76" t="s">
-        <v>556</v>
+        <v>390</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B77" t="s">
-        <v>367</v>
+        <v>225</v>
       </c>
       <c r="C77" t="s">
-        <v>368</v>
+        <v>178</v>
       </c>
       <c r="D77" t="s">
-        <v>505</v>
+        <v>201</v>
       </c>
       <c r="E77" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F77" t="s">
-        <v>560</v>
+        <v>309</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B78" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C78" t="s">
-        <v>339</v>
+        <v>566</v>
       </c>
       <c r="D78" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E78" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="F78" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B79" t="s">
-        <v>568</v>
+        <v>330</v>
       </c>
       <c r="C79" t="s">
-        <v>569</v>
+        <v>331</v>
       </c>
       <c r="D79" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E79" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F79" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B80" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C80" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D80" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E80" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F80" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B81" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C81" t="s">
-        <v>244</v>
+        <v>383</v>
       </c>
       <c r="D81" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E81" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F81" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B82" t="s">
-        <v>584</v>
+        <v>393</v>
       </c>
       <c r="C82" t="s">
-        <v>185</v>
+        <v>394</v>
       </c>
       <c r="D82" t="s">
-        <v>190</v>
+        <v>531</v>
       </c>
       <c r="E82" t="s">
-        <v>417</v>
+        <v>585</v>
       </c>
       <c r="F82" t="s">
-        <v>319</v>
+        <v>586</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B83" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C83" t="s">
-        <v>233</v>
+        <v>358</v>
       </c>
       <c r="D83" t="s">
-        <v>190</v>
+        <v>342</v>
       </c>
       <c r="E83" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F83" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B84" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C84" t="s">
-        <v>368</v>
+        <v>595</v>
       </c>
       <c r="D84" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E84" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F84" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B85" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C85" t="s">
-        <v>185</v>
+        <v>601</v>
       </c>
       <c r="D85" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E85" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="F85" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B86" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C86" t="s">
-        <v>432</v>
+        <v>249</v>
       </c>
       <c r="D86" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E86" t="s">
-        <v>603</v>
+        <v>233</v>
       </c>
       <c r="F86" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B87" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C87" t="s">
-        <v>608</v>
+        <v>178</v>
       </c>
       <c r="D87" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E87" t="s">
-        <v>609</v>
+        <v>443</v>
       </c>
       <c r="F87" t="s">
-        <v>610</v>
+        <v>333</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>611</v>
@@ -5800,105 +5926,105 @@
         <v>613</v>
       </c>
       <c r="C88" t="s">
+        <v>238</v>
+      </c>
+      <c r="D88" t="s">
+        <v>195</v>
+      </c>
+      <c r="E88" t="s">
         <v>614</v>
       </c>
-      <c r="D88" t="s">
-        <v>505</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>615</v>
       </c>
-      <c r="F88" t="s">
+      <c r="H88" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>617</v>
+      </c>
+      <c r="B89" t="s">
         <v>618</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>394</v>
+      </c>
+      <c r="D89" t="s">
+        <v>195</v>
+      </c>
+      <c r="E89" t="s">
         <v>619</v>
       </c>
-      <c r="C89" t="s">
+      <c r="F89" t="s">
         <v>620</v>
       </c>
-      <c r="D89" t="s">
-        <v>196</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="H89" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="F89" t="s">
-        <v>622</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>622</v>
+      </c>
+      <c r="B90" t="s">
+        <v>623</v>
+      </c>
+      <c r="C90" t="s">
+        <v>178</v>
+      </c>
+      <c r="D90" t="s">
+        <v>195</v>
+      </c>
+      <c r="E90" t="s">
         <v>624</v>
       </c>
-      <c r="B90" t="s">
+      <c r="F90" t="s">
         <v>625</v>
       </c>
-      <c r="C90" t="s">
+      <c r="H90" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="D90" t="s">
-        <v>203</v>
-      </c>
-      <c r="E90" t="s">
-        <v>627</v>
-      </c>
-      <c r="F90" t="s">
-        <v>628</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>627</v>
+      </c>
+      <c r="B91" t="s">
+        <v>628</v>
+      </c>
+      <c r="C91" t="s">
+        <v>458</v>
+      </c>
+      <c r="D91" t="s">
+        <v>195</v>
+      </c>
+      <c r="E91" t="s">
+        <v>629</v>
+      </c>
+      <c r="F91" t="s">
         <v>630</v>
       </c>
-      <c r="B91" t="s">
+      <c r="H91" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="C91" t="s">
-        <v>185</v>
-      </c>
-      <c r="D91" t="s">
-        <v>323</v>
-      </c>
-      <c r="E91" t="s">
-        <v>524</v>
-      </c>
-      <c r="F91" t="s">
-        <v>632</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>632</v>
+      </c>
+      <c r="B92" t="s">
+        <v>633</v>
+      </c>
+      <c r="C92" t="s">
         <v>634</v>
       </c>
-      <c r="B92" t="s">
+      <c r="D92" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92" t="s">
         <v>635</v>
-      </c>
-      <c r="C92" t="s">
-        <v>368</v>
-      </c>
-      <c r="D92" t="s">
-        <v>203</v>
-      </c>
-      <c r="E92" t="s">
-        <v>524</v>
       </c>
       <c r="F92" t="s">
         <v>636</v>
@@ -5918,7 +6044,7 @@
         <v>640</v>
       </c>
       <c r="D93" t="s">
-        <v>190</v>
+        <v>531</v>
       </c>
       <c r="E93" t="s">
         <v>641</v>
@@ -5941,105 +6067,105 @@
         <v>646</v>
       </c>
       <c r="D94" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E94" t="s">
-        <v>180</v>
+        <v>647</v>
       </c>
       <c r="F94" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B95" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C95" t="s">
-        <v>233</v>
+        <v>652</v>
       </c>
       <c r="D95" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E95" t="s">
-        <v>442</v>
+        <v>653</v>
       </c>
       <c r="F95" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B96" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C96" t="s">
-        <v>655</v>
+        <v>178</v>
       </c>
       <c r="D96" t="s">
-        <v>203</v>
+        <v>342</v>
       </c>
       <c r="E96" t="s">
-        <v>656</v>
+        <v>550</v>
       </c>
       <c r="F96" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B97" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C97" t="s">
-        <v>661</v>
+        <v>394</v>
       </c>
       <c r="D97" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E97" t="s">
+        <v>550</v>
+      </c>
+      <c r="F97" t="s">
         <v>662</v>
       </c>
-      <c r="F97" t="s">
+      <c r="H97" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>664</v>
+      </c>
+      <c r="B98" t="s">
         <v>665</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>666</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
+        <v>195</v>
+      </c>
+      <c r="E98" t="s">
         <v>667</v>
       </c>
-      <c r="D98" t="s">
-        <v>190</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>668</v>
-      </c>
-      <c r="F98" t="s">
-        <v>246</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>669</v>
@@ -6056,59 +6182,59 @@
         <v>672</v>
       </c>
       <c r="D99" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E99" t="s">
+        <v>180</v>
+      </c>
+      <c r="F99" t="s">
         <v>673</v>
       </c>
-      <c r="F99" t="s">
+      <c r="H99" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>675</v>
+      </c>
+      <c r="B100" t="s">
         <v>676</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" t="s">
+        <v>195</v>
+      </c>
+      <c r="E100" t="s">
+        <v>468</v>
+      </c>
+      <c r="F100" t="s">
         <v>677</v>
       </c>
-      <c r="C100" t="s">
+      <c r="H100" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="D100" t="s">
-        <v>190</v>
-      </c>
-      <c r="E100" t="s">
-        <v>679</v>
-      </c>
-      <c r="F100" t="s">
-        <v>680</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>679</v>
+      </c>
+      <c r="B101" t="s">
+        <v>680</v>
+      </c>
+      <c r="C101" t="s">
+        <v>681</v>
+      </c>
+      <c r="D101" t="s">
+        <v>208</v>
+      </c>
+      <c r="E101" t="s">
         <v>682</v>
       </c>
-      <c r="B101" t="s">
-        <v>568</v>
-      </c>
-      <c r="C101" t="s">
-        <v>569</v>
-      </c>
-      <c r="D101" t="s">
-        <v>190</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>683</v>
-      </c>
-      <c r="F101" t="s">
-        <v>571</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>684</v>
@@ -6125,7 +6251,7 @@
         <v>687</v>
       </c>
       <c r="D102" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E102" t="s">
         <v>688</v>
@@ -6142,183 +6268,183 @@
         <v>691</v>
       </c>
       <c r="B103" t="s">
-        <v>338</v>
+        <v>692</v>
       </c>
       <c r="C103" t="s">
-        <v>339</v>
+        <v>693</v>
       </c>
       <c r="D103" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E103" t="s">
-        <v>445</v>
+        <v>694</v>
       </c>
       <c r="F103" t="s">
-        <v>341</v>
+        <v>251</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B104" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C104" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D104" t="s">
-        <v>505</v>
+        <v>195</v>
       </c>
       <c r="E104" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="F104" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="B105" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="C105" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="D105" t="s">
-        <v>505</v>
+        <v>195</v>
       </c>
       <c r="E105" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="F105" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="B106" t="s">
-        <v>703</v>
+        <v>594</v>
       </c>
       <c r="C106" t="s">
-        <v>411</v>
+        <v>595</v>
       </c>
       <c r="D106" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E106" t="s">
-        <v>536</v>
+        <v>709</v>
       </c>
       <c r="F106" t="s">
-        <v>704</v>
+        <v>597</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="B107" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C107" t="s">
-        <v>185</v>
+        <v>713</v>
       </c>
       <c r="D107" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E107" t="s">
-        <v>708</v>
+        <v>180</v>
       </c>
       <c r="F107" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="B108" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="C108" t="s">
-        <v>411</v>
+        <v>718</v>
       </c>
       <c r="D108" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E108" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="F108" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="B109" t="s">
-        <v>717</v>
+        <v>357</v>
       </c>
       <c r="C109" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D109" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E109" t="s">
-        <v>718</v>
+        <v>471</v>
       </c>
       <c r="F109" t="s">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B110" t="s">
-        <v>220</v>
+        <v>725</v>
       </c>
       <c r="C110" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="D110" t="s">
-        <v>190</v>
+        <v>531</v>
       </c>
       <c r="E110" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="F110" t="s">
-        <v>364</v>
+        <v>728</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -6326,341 +6452,341 @@
         <v>724</v>
       </c>
       <c r="B111" t="s">
-        <v>310</v>
+        <v>725</v>
       </c>
       <c r="C111" t="s">
-        <v>311</v>
+        <v>730</v>
       </c>
       <c r="D111" t="s">
-        <v>190</v>
+        <v>531</v>
       </c>
       <c r="E111" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F111" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="B112" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="C112" t="s">
-        <v>730</v>
+        <v>437</v>
       </c>
       <c r="D112" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E112" t="s">
-        <v>731</v>
+        <v>562</v>
       </c>
       <c r="F112" t="s">
-        <v>622</v>
+        <v>735</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B113" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C113" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D113" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E113" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="F113" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B114" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C114" t="s">
-        <v>740</v>
+        <v>437</v>
       </c>
       <c r="D114" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E114" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="F114" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="B115" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="C115" t="s">
-        <v>744</v>
+        <v>394</v>
       </c>
       <c r="D115" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E115" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="F115" t="s">
-        <v>742</v>
+        <v>180</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="B116" t="s">
-        <v>747</v>
+        <v>225</v>
       </c>
       <c r="C116" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D116" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E116" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="F116" t="s">
-        <v>750</v>
+        <v>390</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B117" t="s">
-        <v>753</v>
+        <v>324</v>
       </c>
       <c r="C117" t="s">
-        <v>754</v>
+        <v>325</v>
       </c>
       <c r="D117" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E117" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F117" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B118" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C118" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D118" t="s">
-        <v>505</v>
+        <v>195</v>
       </c>
       <c r="E118" t="s">
-        <v>449</v>
+        <v>762</v>
       </c>
       <c r="F118" t="s">
-        <v>319</v>
+        <v>648</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B119" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C119" t="s">
-        <v>764</v>
+        <v>178</v>
       </c>
       <c r="D119" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E119" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F119" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B120" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C120" t="s">
-        <v>233</v>
+        <v>771</v>
       </c>
       <c r="D120" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E120" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="F120" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B121" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C121" t="s">
         <v>775</v>
       </c>
       <c r="D121" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E121" t="s">
+        <v>772</v>
+      </c>
+      <c r="F121" t="s">
+        <v>773</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="F121" t="s">
-        <v>180</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>777</v>
+      </c>
+      <c r="B122" t="s">
         <v>778</v>
       </c>
-      <c r="B122" t="s">
-        <v>774</v>
-      </c>
       <c r="C122" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D122" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E122" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F122" t="s">
-        <v>180</v>
+        <v>781</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B123" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C123" t="s">
-        <v>432</v>
+        <v>785</v>
       </c>
       <c r="D123" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E123" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="F123" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B124" t="s">
-        <v>787</v>
+        <v>363</v>
       </c>
       <c r="C124" t="s">
-        <v>357</v>
+        <v>238</v>
       </c>
       <c r="D124" t="s">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="E124" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F124" t="s">
-        <v>307</v>
+        <v>365</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B125" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C125" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D125" t="s">
-        <v>190</v>
+        <v>531</v>
       </c>
       <c r="E125" t="s">
-        <v>793</v>
+        <v>475</v>
       </c>
       <c r="F125" t="s">
-        <v>794</v>
+        <v>333</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>795</v>
@@ -6677,7 +6803,7 @@
         <v>798</v>
       </c>
       <c r="D126" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E126" t="s">
         <v>799</v>
@@ -6697,16 +6823,16 @@
         <v>803</v>
       </c>
       <c r="C127" t="s">
+        <v>238</v>
+      </c>
+      <c r="D127" t="s">
+        <v>195</v>
+      </c>
+      <c r="E127" t="s">
         <v>804</v>
       </c>
-      <c r="D127" t="s">
-        <v>190</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>805</v>
-      </c>
-      <c r="F127" t="s">
-        <v>180</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>806</v>
@@ -6714,94 +6840,255 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="B128" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="C128" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D128" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E128" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="F128" t="s">
         <v>180</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>812</v>
+      </c>
+      <c r="B129" t="s">
+        <v>808</v>
+      </c>
+      <c r="C129" t="s">
         <v>809</v>
       </c>
-      <c r="B129" t="s">
-        <v>194</v>
-      </c>
-      <c r="C129" t="s">
-        <v>195</v>
-      </c>
       <c r="D129" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E129" t="s">
-        <v>197</v>
+        <v>813</v>
       </c>
       <c r="F129" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="B130" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="C130" t="s">
-        <v>813</v>
+        <v>458</v>
       </c>
       <c r="D130" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E130" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="F130" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B131" t="s">
-        <v>580</v>
+        <v>821</v>
       </c>
       <c r="C131" t="s">
-        <v>244</v>
+        <v>383</v>
       </c>
       <c r="D131" t="s">
+        <v>342</v>
+      </c>
+      <c r="E131" t="s">
+        <v>822</v>
+      </c>
+      <c r="F131" t="s">
+        <v>321</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>824</v>
+      </c>
+      <c r="B132" t="s">
+        <v>825</v>
+      </c>
+      <c r="C132" t="s">
+        <v>826</v>
+      </c>
+      <c r="D132" t="s">
+        <v>195</v>
+      </c>
+      <c r="E132" t="s">
+        <v>827</v>
+      </c>
+      <c r="F132" t="s">
+        <v>828</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>830</v>
+      </c>
+      <c r="B133" t="s">
+        <v>831</v>
+      </c>
+      <c r="C133" t="s">
+        <v>832</v>
+      </c>
+      <c r="D133" t="s">
+        <v>195</v>
+      </c>
+      <c r="E133" t="s">
+        <v>833</v>
+      </c>
+      <c r="F133" t="s">
+        <v>834</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>836</v>
+      </c>
+      <c r="B134" t="s">
+        <v>837</v>
+      </c>
+      <c r="C134" t="s">
+        <v>838</v>
+      </c>
+      <c r="D134" t="s">
+        <v>195</v>
+      </c>
+      <c r="E134" t="s">
+        <v>839</v>
+      </c>
+      <c r="F134" t="s">
+        <v>180</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>836</v>
+      </c>
+      <c r="B135" t="s">
+        <v>837</v>
+      </c>
+      <c r="C135" t="s">
+        <v>841</v>
+      </c>
+      <c r="D135" t="s">
+        <v>195</v>
+      </c>
+      <c r="E135" t="s">
+        <v>839</v>
+      </c>
+      <c r="F135" t="s">
+        <v>180</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>843</v>
+      </c>
+      <c r="B136" t="s">
+        <v>199</v>
+      </c>
+      <c r="C136" t="s">
+        <v>200</v>
+      </c>
+      <c r="D136" t="s">
+        <v>201</v>
+      </c>
+      <c r="E136" t="s">
+        <v>202</v>
+      </c>
+      <c r="F136" t="s">
         <v>203</v>
       </c>
-      <c r="E131" t="s">
-        <v>818</v>
-      </c>
-      <c r="F131" t="s">
-        <v>581</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>819</v>
+      <c r="H136" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>845</v>
+      </c>
+      <c r="B137" t="s">
+        <v>846</v>
+      </c>
+      <c r="C137" t="s">
+        <v>847</v>
+      </c>
+      <c r="D137" t="s">
+        <v>195</v>
+      </c>
+      <c r="E137" t="s">
+        <v>848</v>
+      </c>
+      <c r="F137" t="s">
+        <v>849</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>851</v>
+      </c>
+      <c r="B138" t="s">
+        <v>606</v>
+      </c>
+      <c r="C138" t="s">
+        <v>249</v>
+      </c>
+      <c r="D138" t="s">
+        <v>208</v>
+      </c>
+      <c r="E138" t="s">
+        <v>852</v>
+      </c>
+      <c r="F138" t="s">
+        <v>607</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -6937,6 +7224,13 @@
     <hyperlink ref="H129" r:id="rId128"/>
     <hyperlink ref="H130" r:id="rId129"/>
     <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
